--- a/stories/arbres/TREE-COL-001.xlsx
+++ b/stories/arbres/TREE-COL-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans la cuisine, avec maman. Papa coupe une pomme. Des copains vont arriver. On va dire des mots gentils. Maman dit : on dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Sami est dans la cuisine, avec maman. Papa coupe une pomme. Des copains vont arriver. On va dire des mots gentils. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est dans la cuisine, avec maman. Papa coupe une pomme. Des copains vont arriver. On va dire des mots gentils.
+maman|On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami entend le train, tout loin. Un copain entre. Sami dit bonjour. Il tend une pomme. Il dit s'il te plaît. Le copain dit merci. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On dit bonjour, s'il te plaît, merci ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami respire. Papa est là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2185,6 +2228,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2349,6 +2397,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à Tom. Il demande le train en bois : s'il te plaît. Tom dit merci. C'est le matin. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2588,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le train. Puis Tom. Puis le matin. Un crochet tient bien le manteau. Sami marche près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Ça sent le pain chaud. Sami boit une gorgée d'eau. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami se souvient de le train. Et de Tom. Et de le soir. Les chaussures font toc toc. Sami tend le soir à maman. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3619,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est après la sieste. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est après la sieste. Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3757,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est après la sieste.
+papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3949,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4116,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le train. Sami s'arrête. Un vélo passe au loin. Sami chuchote : c'est fini. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4283,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4450,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range Léa. après la sieste reste près de le train. Le savon sent bon. Sami écoute papa encore une fois. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4617,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4646,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>Le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4784,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4951,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5118,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est le soir. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5309,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5476,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Sami est rangé. le train est fini. Une chaussette est encore sablée. Sami ferme le sac. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5643,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5810,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Sami pose Sami. le train est derrière. On rit un peu. Sami dit merci à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5977,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6144,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre le soir. Papa a vu le train. Et Sami. Un linge sèche à l'air. Sami pose Sami à sa place. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6311,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6478,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami entend le bus. Une copine entre. Sami dit bonjour. Il demande le torchon : s'il te plaît. Il dit merci. Papa coupe encore une pomme.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6659,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Quel mot dit-on pour demander ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6832,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami retient le geste. Papa sourit. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7027,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6867,7 +7056,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le matin. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le matin. Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7005,6 +7194,12 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le matin.
+papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7386,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7553,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi le bus. Puis Tom. Puis le matin. Un ruban reste dans la poche. Sami essuie ses mains. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7720,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7887,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Un chat miaule une fois. Sami range la tasse. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8054,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7863,7 +8083,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de le bus. Et de Tom. Et de le soir. Un ballon s'immobilise. Sami dit : j'ai appris. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>Sami se souvient de le bus. Et de Tom. Et de le soir. Un ballon s'immobilise. J'ai appris. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8001,6 +8221,13 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami se souvient de le bus. Et de Tom. Et de le soir. Un ballon s'immobilise.
+enfant-m|J'ai appris. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci.
+narrateur|Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8390,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8557,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est après la sieste. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8748,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8915,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le bus. Sami s'arrête. On dit merci. Maman n'est pas loin. Sami les rejoint. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9082,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9249,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range Léa. après la sieste reste près de le bus. On se tient la main. Sami souffle, puis sourit à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9416,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9183,7 +9445,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>Le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9321,6 +9583,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9750,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9917,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le soir. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10108,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10275,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Sami est rangé. le bus est fini. L'eau coule, tout petit bruit. Sami prend la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10442,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10609,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Sami pose Sami. le bus est derrière. Une pomme brille un peu. Sami caresse le doudou. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10776,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10943,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre le soir. Papa a vu le bus. Et Sami. Une tasse cliquette. Sami enfile ses chaussons. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11110,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10965,6 +11277,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami entend une voiture. Un copain entre. Sami dit bonjour. Il demande une part : s'il te plaît. Il dit merci. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11462,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On dit merci ?</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11635,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami hoche la tête. On continue, avec papa. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11501,6 +11828,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11665,6 +11997,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le matin. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11851,6 +12188,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12013,6 +12355,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a choisi la voiture. Puis Tom. Puis le matin. On range un objet. Sami répète tout bas le geste. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12175,6 +12522,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12337,6 +12689,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Il y a des miettes sur la table. Sami pose sa tête un moment. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12499,6 +12856,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12661,6 +13023,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami se souvient de la voiture. Et de Tom. Et de le soir. Un galet est encore chaud. Sami plie un pull. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12823,6 +13190,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12985,6 +13357,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est après la sieste. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13171,6 +13548,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13333,6 +13715,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Sami s'arrête. On attend son tour. Sami s'assoit près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13495,6 +13882,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13657,6 +14049,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami range Léa. après la sieste reste près de la voiture. La lumière est claire. Sami serre la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13819,6 +14216,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13843,7 +14245,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>Le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13981,6 +14383,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14143,6 +14550,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14167,7 +14579,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le soir. Papa dit : je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le soir. Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14305,6 +14717,12 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le soir.
+papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14491,6 +14909,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14653,6 +15076,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami rejoint le matin. Sami est rangé. la voiture est fini. Le vent est doux. Sami ferme la porte, tout doux. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14815,6 +15243,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14977,6 +15410,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Sami pose Sami. la voiture est derrière. Le sol est un peu froid. Sami montre après la sieste à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15139,6 +15577,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15301,6 +15744,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami montre le soir. Papa a vu la voiture. Et Sami. On souffle doucement. Sami range la voiture dans sa tête, comme un souvenir. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15463,6 +15911,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15481,7 +15934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15512,6 +15965,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-001.xlsx
+++ b/stories/arbres/TREE-COL-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Sami entend le train, tout loin. Un copain entre. Sami dit bonjour. Il tend une pomme. Il dit s'il te plaît. Le copain dit merci. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|On dit bonjour, s'il te plaît, merci ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami respire. Papa est là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2235,6 +2245,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2402,6 +2413,7 @@
           <t>narrateur|Sami dit bonjour à Tom. Il demande le train en bois : s'il te plaît. Tom dit merci. C'est le matin. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Sami a choisi le train. Puis Tom. Puis le matin. Un crochet tient bien le manteau. Sami marche près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Ça sent le pain chaud. Sami boit une gorgée d'eau. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Sami se souvient de le train. Et de Tom. Et de le soir. Les chaussures font toc toc. Sami tend le soir à maman. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3763,6 +3782,7 @@
 papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3954,6 +3974,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4121,6 +4142,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le train. Sami s'arrête. Un vélo passe au loin. Sami chuchote : c'est fini. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4288,6 +4310,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4455,6 +4478,7 @@
           <t>narrateur|Sami range Léa. après la sieste reste près de le train. Le savon sent bon. Sami écoute papa encore une fois. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4622,6 +4646,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4789,6 +4814,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4956,6 +4982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5123,6 +5150,7 @@
           <t>narrateur|Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est le soir. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5314,6 +5342,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5481,6 +5510,7 @@
           <t>narrateur|Sami rejoint le matin. Sami est rangé. le train est fini. Une chaussette est encore sablée. Sami ferme le sac. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5648,6 +5678,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5815,6 +5846,7 @@
           <t>narrateur|Près de après la sieste. Sami pose Sami. le train est derrière. On rit un peu. Sami dit merci à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5982,6 +6014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6149,6 +6182,7 @@
           <t>narrateur|Sami montre le soir. Papa a vu le train. Et Sami. Un linge sèche à l'air. Sami pose Sami à sa place. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6316,6 +6350,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6483,6 +6518,7 @@
           <t>narrateur|Sami entend le bus. Une copine entre. Sami dit bonjour. Il demande le torchon : s'il te plaît. Il dit merci. Papa coupe encore une pomme.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6666,6 +6702,7 @@
           <t>narrateur|Quel mot dit-on pour demander ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6837,6 +6874,7 @@
           <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami retient le geste. Papa sourit. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7032,6 +7070,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7200,6 +7239,7 @@
 papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7391,6 +7431,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7558,6 +7599,7 @@
           <t>narrateur|Sami a choisi le bus. Puis Tom. Puis le matin. Un ruban reste dans la poche. Sami essuie ses mains. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7725,6 +7767,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7892,6 +7935,7 @@
           <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Un chat miaule une fois. Sami range la tasse. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8059,6 +8103,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8228,6 +8273,7 @@
 narrateur|Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8395,6 +8441,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8562,6 +8609,7 @@
           <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est après la sieste. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8753,6 +8801,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8920,6 +8969,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le bus. Sami s'arrête. On dit merci. Maman n'est pas loin. Sami les rejoint. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9087,6 +9137,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9254,6 +9305,7 @@
           <t>narrateur|Sami range Léa. après la sieste reste près de le bus. On se tient la main. Sami souffle, puis sourit à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9421,6 +9473,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9588,6 +9641,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9755,6 +9809,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9922,6 +9977,7 @@
           <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le soir. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10113,6 +10169,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10280,6 +10337,7 @@
           <t>narrateur|Sami rejoint le matin. Sami est rangé. le bus est fini. L'eau coule, tout petit bruit. Sami prend la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10447,6 +10505,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10614,6 +10673,7 @@
           <t>narrateur|Près de après la sieste. Sami pose Sami. le bus est derrière. Une pomme brille un peu. Sami caresse le doudou. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10781,6 +10841,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10948,6 +11009,7 @@
           <t>narrateur|Sami montre le soir. Papa a vu le bus. Et Sami. Une tasse cliquette. Sami enfile ses chaussons. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11115,6 +11177,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11282,6 +11345,11 @@
           <t>narrateur|Sami entend une voiture. Un copain entre. Sami dit bonjour. Il demande une part : s'il te plaît. Il dit merci. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11469,6 +11537,7 @@
           <t>narrateur|On dit merci ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11640,6 +11709,7 @@
           <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami hoche la tête. On continue, avec papa. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11835,6 +11905,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12002,6 +12073,7 @@
           <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le matin. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12193,6 +12265,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12360,6 +12433,7 @@
           <t>narrateur|Sami a choisi la voiture. Puis Tom. Puis le matin. On range un objet. Sami répète tout bas le geste. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12527,6 +12601,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12694,6 +12769,7 @@
           <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Il y a des miettes sur la table. Sami pose sa tête un moment. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12861,6 +12937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13028,6 +13105,7 @@
           <t>narrateur|Sami se souvient de la voiture. Et de Tom. Et de le soir. Un galet est encore chaud. Sami plie un pull. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13195,6 +13273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13362,6 +13441,7 @@
           <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est après la sieste. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13553,6 +13633,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13720,6 +13801,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Sami s'arrête. On attend son tour. Sami s'assoit près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13887,6 +13969,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14054,6 +14137,7 @@
           <t>narrateur|Sami range Léa. après la sieste reste près de la voiture. La lumière est claire. Sami serre la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14221,6 +14305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14388,6 +14473,7 @@
           <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14555,6 +14641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14723,6 +14810,7 @@
 papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14914,6 +15002,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15081,6 +15170,7 @@
           <t>narrateur|Sami rejoint le matin. Sami est rangé. la voiture est fini. Le vent est doux. Sami ferme la porte, tout doux. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15248,6 +15338,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15415,6 +15506,7 @@
           <t>narrateur|Près de après la sieste. Sami pose Sami. la voiture est derrière. Le sol est un peu froid. Sami montre après la sieste à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15582,6 +15674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15749,6 +15842,7 @@
           <t>narrateur|Sami montre le soir. Papa a vu la voiture. Et Sami. On souffle doucement. Sami range la voiture dans sa tête, comme un souvenir. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15916,6 +16010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15934,7 +16029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15972,6 +16067,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15986,7 +16095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16173,6 +16282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-001.xlsx
+++ b/stories/arbres/TREE-COL-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bonjour, s'il te plaît, merci — dans la cuisine</t>
+          <t>La casserole et les pommes de Raphaël</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La casserole chante. Raphaël prépare des pommes pour Mila. Il dit bonjour, s'il te plaît, merci, avec le train, le bus ou la voiture.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans la cuisine, avec maman. Papa coupe une pomme. Des copains vont arriver. On va dire des mots gentils. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil pose sur le carrelage. Les chaussons de Raphaël attendent sous la table. La casserole chante un peu, Raphaël. Tu as vu le torchon ? Il est tout rayé. Oui. Il est rouge et blanc. Papa pose des rondelles dans un bol jaune. Le bois de la planche est lisse, un peu humide. En ce moment, Raphaël est dans la cuisine. Il tient une cuillère en bois. Mila va arriver tout à l'heure. On dit bonjour, d'accord ? Bonjour. Et si tu veux une pomme ? S'il te plaît. Bravo. Et après ? Merci. Bonjour. S'il te plaît. Merci. Le train en bois attend sous la table. Le bus rouge est près du tabouret. La petite voiture brille. Mila aime les mots gentils. Toi aussi, tu les connais. Oui, papa. Une pelure de pomme fait un petit colimaçon. Tu es prêt ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sami est dans la cuisine, avec maman. Papa coupe une pomme. Des copains vont arriver. On va dire des mots gentils.
-maman|On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une goutte glisse le long de la casserole.
+narrateur|Ça sent la pomme, toute douce.
+narrateur|Le torchon rayé pend près de l'évier.
+narrateur|Dehors, le marché parle tout bas.
+narrateur|Un rond de soleil pose sur le carrelage.
+narrateur|Les chaussons de Raphaël attendent sous la table.
+papa|La casserole chante un peu, Raphaël.
+maman|Tu as vu le torchon ?
+enfant-m|Il est tout rayé.
+maman|Oui.
+maman|Il est rouge et blanc.
+narrateur|Papa pose des rondelles dans un bol jaune.
+narrateur|Le bois de la planche est lisse, un peu humide.
+narrateur|En ce moment, Raphaël est dans la cuisine.
+narrateur|Il tient une cuillère en bois.
+narrateur|Mila va arriver tout à l'heure.
+maman|On dit bonjour, d'accord ?
+enfant-m|Bonjour.
+papa|Et si tu veux une pomme ?
+enfant-m|S'il te plaît.
+maman|Bravo.
+maman|Et après ?
+enfant-m|Merci.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Le train en bois attend sous la table.
+narrateur|Le bus rouge est près du tabouret.
+narrateur|La petite voiture brille.
+maman|Mila aime les mots gentils.
+papa|Toi aussi, tu les connais.
+enfant-m|Oui, papa.
+narrateur|Une pelure de pomme fait un petit colimaçon.
+maman|Tu es prêt ?
+enfant-m|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>casserole,pomme</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1403,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le train, le bus, ou la voiture.</t>
+          <t>Qu'est-ce que Raphaël prend ? Le train, le bus, ou la voiture.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1567,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le train, le bus, ou la voiture.</t>
+          <t>narrateur|Qu'est-ce que Raphaël prend ?
+maman|Le train, le bus, ou la voiture.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami entend le train, tout loin. Un copain entre. Sami dit bonjour. Il tend une pomme. Il dit s'il te plaît. Le copain dit merci. Maman sourit.</t>
+          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte s'ouvre, tout doux. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Bonjour, Mila. Tu veux une rondelle ? S'il te plaît. Papa tend une pomme, toute lisse. Merci. Merci, papa. Bravo, Raphaël. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le train reste près du bol jaune.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,10 +1736,31 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami entend le train, tout loin. Un copain entre. Sami dit bonjour. Il tend une pomme. Il dit s'il te plaît. Le copain dit merci. Maman sourit.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël prend le train en bois.
+narrateur|Les roues font un petit clic sur le carrelage.
+narrateur|La porte s'ouvre, tout doux.
+narrateur|Mila entre, les joues roses.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour, Raphaël.
+maman|Bonjour, Mila.
+papa|Tu veux une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|Papa tend une pomme, toute lisse.
+enfant-f|Merci.
+enfant-m|Merci, papa.
+maman|Bravo, Raphaël.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Le train reste près du bol jaune.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>train_bois,porte</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1902,7 +1973,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Bonjour, s'il te plaît, merci. Sami respire. Papa est là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Oui. Bonjour. S'il te plaît. Merci. Raphaël respire, tout calme. Bravo, Raphaël. Tu as fait du bon travail. Merci, papa. On continue, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2117,15 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami respire. Papa est là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>narrateur|Oui.
+maman|Bonjour.
+maman|S'il te plaît.
+maman|Merci.
+narrateur|Raphaël respire, tout calme.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+maman|On continue, tout doux.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2153,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On va où, dans la cuisine ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2242,7 +2321,8 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On va où, dans la cuisine ?
+papa|La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2270,7 +2350,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Tom. Il demande le train en bois : s'il te plaît. Tom dit merci. C'est le matin. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël pose le train en bois près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Bonjour, Mila. Bonjour. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Bravo. Tu as dit les mots. S'il te plaît. Une pomme. Voilà. Merci d'avoir demandé. Une rondelle brille dans l'assiette. Les mots gentils, à table aussi.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2410,10 +2490,30 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à Tom. Il demande le train en bois : s'il te plaît. Tom dit merci. C'est le matin. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Raphaël pose le train en bois près de la table.
+narrateur|Le bol jaune est au milieu.
+narrateur|Mila tire une chaise, tout doux.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+maman|Une assiette, Raphaël ?
+enfant-m|S'il te plaît.
+narrateur|L'assiette est ronde, un peu froide.
+enfant-m|Merci, maman.
+papa|Bravo.
+papa|Tu as dit les mots.
+enfant-f|S'il te plaît.
+enfant-f|Une pomme.
+papa|Voilà.
+papa|Merci d'avoir demandé.
+narrateur|Une rondelle brille dans l'assiette.
+maman|Les mots gentils, à table aussi.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2438,7 +2538,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2702,8 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2731,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le train. Puis Tom. Puis le matin. Un crochet tient bien le manteau. Sami marche près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. Le soleil touche une roue du train, sur la table. Ça sent le lait et la pomme. Raphaël est près de la table, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,10 +2871,30 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le train. Puis Tom. Puis le matin. Un crochet tient bien le manteau. Sami marche près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|Le soleil touche une roue du train, sur la table.
+narrateur|Ça sent le lait et la pomme.
+narrateur|Raphaël est près de la table, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2798,7 +2919,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de la table. Il a joué avec le train en bois, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3059,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de la table.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3096,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de après la sieste. Tom est rangé. Ça sent le pain chaud. Sami boit une gorgée d'eau. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. Le train dort encore sur la table. Ça sent le pain chaud. Raphaël est près de la table, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,10 +3236,30 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Ça sent le pain chaud. Sami boit une gorgée d'eau. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Le train dort encore sur la table.
+narrateur|Ça sent le pain chaud.
+narrateur|Raphaël est près de la table, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3134,7 +3284,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de la table. Il a joué avec le train en bois, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3424,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de la table.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3461,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de le train. Et de Tom. Et de le soir. Les chaussures font toc toc. Sami tend le soir à maman. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. Une lampe jaune pose un rond sur la table. Le train brille tout doux. Raphaël est près de la table, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,10 +3601,30 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sami se souvient de le train. Et de Tom. Et de le soir. Les chaussures font toc toc. Sami tend le soir à maman. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Une lampe jaune pose un rond sur la table.
+narrateur|Le train brille tout doux.
+narrateur|Raphaël est près de la table, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3470,7 +3649,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de la table. Il a joué avec le train en bois, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3789,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de la table.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3826,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est après la sieste. Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël va près de la fenêtre, avec le train en bois. La vitre est un peu floue. Mila trace un petit rond du doigt. Bonjour, Mila. Bonjour. Tu veux le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Bravo, Raphaël. Merci. Je vois le marché. On dit les mots, même près de la fenêtre. Bonjour. S'il te plaît. Merci. Un oiseau passe derrière la vitre.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,11 +3966,30 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est après la sieste.
-papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Raphaël va près de la fenêtre, avec le train en bois.
+narrateur|La vitre est un peu floue.
+narrateur|Mila trace un petit rond du doigt.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux le torchon, pour la vitre ?
+enfant-m|S'il te plaît.
+narrateur|Le torchon est doux, un peu épais.
+enfant-m|Merci, papa.
+maman|Bravo, Raphaël.
+enfant-f|Merci.
+enfant-f|Je vois le marché.
+maman|On dit les mots, même près de la fenêtre.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Un oiseau passe derrière la vitre.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>vitre</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3807,7 +4014,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3971,7 +4178,8 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3999,7 +4207,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le train. Sami s'arrête. Un vélo passe au loin. Sami chuchote : c'est fini. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. La vitre est froide sous le doigt. Le train attend près de la fenêtre. Raphaël est près de la fenêtre, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4139,10 +4347,30 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le train. Sami s'arrête. Un vélo passe au loin. Sami chuchote : c'est fini. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La vitre est froide sous le doigt.
+narrateur|Le train attend près de la fenêtre.
+narrateur|Raphaël est près de la fenêtre, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4167,7 +4395,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de la fenêtre. Il a joué avec le train en bois, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4307,7 +4535,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de la fenêtre.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4335,7 +4572,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sami range Léa. après la sieste reste près de le train. Le savon sent bon. Sami écoute papa encore une fois. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. Un rayon paresseux traverse la fenêtre. Le train est tiède. Raphaël est près de la fenêtre, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4475,10 +4712,30 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sami range Léa. après la sieste reste près de le train. Le savon sent bon. Sami écoute papa encore une fois. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Un rayon paresseux traverse la fenêtre.
+narrateur|Le train est tiède.
+narrateur|Raphaël est près de la fenêtre, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,7 +4760,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de la fenêtre. Il a joué avec le train en bois, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4643,7 +4900,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de la fenêtre.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4671,7 +4937,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. Dehors, le marché s'est tu. Le train repose près de la vitre sombre. Raphaël est près de la fenêtre, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4811,10 +5077,30 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le train reste dans le souvenir. Une feuille tombe. Sami raccroche un linge. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Dehors, le marché s'est tu.
+narrateur|Le train repose près de la vitre sombre.
+narrateur|Raphaël est près de la fenêtre, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,7 +5125,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de la fenêtre. Il a joué avec le train en bois, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4979,7 +5265,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de la fenêtre.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5007,7 +5302,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est le soir. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël glisse le train en bois près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Bonjour, Mila. Bonjour. Tu veux le tabouret, Raphaël ? S'il te plaît. Tu peux. Merci. Raphaël pose une main sur le bois lisse. Bravo. Tu as demandé. Merci, Mila. Les trois mots, même pour un tabouret. Bonjour. S'il te plaît. Merci. Le tabouret fait un tout petit craquement.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5147,10 +5442,31 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à Tom. Il demande le train : s'il te plaît. Tom dit merci. C'est le soir. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Raphaël glisse le train en bois près du tabouret.
+narrateur|Le tabouret est bas, en bois clair.
+narrateur|Mila s'assoit, les pieds qui balancent.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+maman|Tu veux le tabouret, Raphaël ?
+enfant-m|S'il te plaît.
+enfant-f|Tu peux.
+enfant-f|Merci.
+narrateur|Raphaël pose une main sur le bois lisse.
+papa|Bravo.
+papa|Tu as demandé.
+enfant-m|Merci, Mila.
+maman|Les trois mots, même pour un tabouret.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Le tabouret fait un tout petit craquement.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>bois</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,7 +5491,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5339,7 +5655,8 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5367,7 +5684,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Sami est rangé. le train est fini. Une chaussette est encore sablée. Sami ferme le sac. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. Le tabouret est un peu froid. Le train passe entre les pieds de Mila. Raphaël est près de le tabouret, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5507,10 +5824,30 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Sami est rangé. le train est fini. Une chaussette est encore sablée. Sami ferme le sac. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|Le tabouret est un peu froid.
+narrateur|Le train passe entre les pieds de Mila.
+narrateur|Raphaël est près de le tabouret, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5535,7 +5872,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de le tabouret. Il a joué avec le train en bois, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5675,7 +6012,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de le tabouret.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5703,7 +6049,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sami pose Sami. le train est derrière. On rit un peu. Sami dit merci à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. Le tabouret a gardé un peu de chaleur. Le train fait clic, tout bas. Raphaël est près de le tabouret, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5843,10 +6189,30 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Sami pose Sami. le train est derrière. On rit un peu. Sami dit merci à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Le tabouret a gardé un peu de chaleur.
+narrateur|Le train fait clic, tout bas.
+narrateur|Raphaël est près de le tabouret, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5871,7 +6237,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de le tabouret. Il a joué avec le train en bois, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6011,7 +6377,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de le tabouret.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6039,7 +6414,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sami montre le soir. Papa a vu le train. Et Sami. Un linge sèche à l'air. Sami pose Sami à sa place. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. Le tabouret craque, tout petit. Le train rentre sous la chaise. Raphaël est près de le tabouret, avec le train. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6179,10 +6554,30 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sami montre le soir. Papa a vu le train. Et Sami. Un linge sèche à l'air. Sami pose Sami à sa place. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Le tabouret craque, tout petit.
+narrateur|Le train rentre sous la chaise.
+narrateur|Raphaël est près de le tabouret, avec le train.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6207,7 +6602,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de le tabouret. Il a joué avec le train en bois, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6347,7 +6742,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de le tabouret.
+narrateur|Il a joué avec le train en bois, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6375,7 +6779,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sami entend le bus. Une copine entre. Sami dit bonjour. Il demande le torchon : s'il te plaît. Il dit merci. Papa coupe encore une pomme.</t>
+          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte de la cuisine. Bonjour, Mila. Bonjour. Bonjour, Mila. Raphaël veut le torchon rayé. S'il te plaît. Voilà le torchon. Merci, maman. Merci. Bravo. Tu as demandé, puis remercié. On dit aussi bonjour. Bonjour. Le bus rouge attend près du tabouret.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6515,10 +6919,29 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sami entend le bus. Une copine entre. Sami dit bonjour. Il demande le torchon : s'il te plaît. Il dit merci. Papa coupe encore une pomme.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Raphaël prend le bus rouge.
+narrateur|Dehors, un vrai bus passe, tout bas.
+narrateur|Mila pousse la porte de la cuisine.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Bonjour, Mila.
+narrateur|Raphaël veut le torchon rayé.
+enfant-m|S'il te plaît.
+maman|Voilà le torchon.
+enfant-m|Merci, maman.
+enfant-f|Merci.
+maman|Bravo.
+maman|Tu as demandé, puis remercié.
+papa|On dit aussi bonjour.
+enfant-m|Bonjour.
+narrateur|Le bus rouge attend près du tabouret.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>bus,porte</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6543,7 +6966,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Quel mot dit-on pour demander ?</t>
+          <t>Raphaël veut le torchon. Que dit-il ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6699,7 +7122,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Quel mot dit-on pour demander ?</t>
+          <t>narrateur|Raphaël veut le torchon.
+narrateur|Que dit-il ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6727,7 +7151,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Bonjour, s'il te plaît, merci. Sami retient le geste. Papa sourit. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Oui. On dit s'il te plaît. Et bonjour. Et merci. Raphaël tient le torchon rayé. Bravo. Tu as demandé gentiment. S'il te plaît. C'est ça.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6871,7 +7295,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami retient le geste. Papa sourit. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>narrateur|Oui.
+papa|On dit s'il te plaît.
+maman|Et bonjour.
+maman|Et merci.
+narrateur|Raphaël tient le torchon rayé.
+papa|Bravo.
+papa|Tu as demandé gentiment.
+enfant-m|S'il te plaît.
+maman|C'est ça.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6899,7 +7331,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On va où, dans la cuisine ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7067,7 +7499,8 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On va où, dans la cuisine ?
+papa|La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7095,7 +7528,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le matin. Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël pose le bus rouge près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Bonjour, Mila. Bonjour. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Bravo. Tu as dit les mots. S'il te plaît. Une pomme. Voilà. Merci d'avoir demandé. Une rondelle brille dans l'assiette. Les mots gentils, à table aussi.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7235,11 +7668,30 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le matin.
-papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Raphaël pose le bus rouge près de la table.
+narrateur|Le bol jaune est au milieu.
+narrateur|Mila tire une chaise, tout doux.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+maman|Une assiette, Raphaël ?
+enfant-m|S'il te plaît.
+narrateur|L'assiette est ronde, un peu froide.
+enfant-m|Merci, maman.
+papa|Bravo.
+papa|Tu as dit les mots.
+enfant-f|S'il te plaît.
+enfant-f|Une pomme.
+papa|Voilà.
+papa|Merci d'avoir demandé.
+narrateur|Une rondelle brille dans l'assiette.
+maman|Les mots gentils, à table aussi.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7264,7 +7716,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7428,7 +7880,8 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7456,7 +7909,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi le bus. Puis Tom. Puis le matin. Un ruban reste dans la poche. Sami essuie ses mains. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. Le bus rouge est sur la table, près du bol. Une miette de pain brille. Raphaël est près de la table, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7596,10 +8049,30 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi le bus. Puis Tom. Puis le matin. Un ruban reste dans la poche. Sami essuie ses mains. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|Le bus rouge est sur la table, près du bol.
+narrateur|Une miette de pain brille.
+narrateur|Raphaël est près de la table, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7624,7 +8097,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de la table. Il a joué avec le bus rouge, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7764,7 +8237,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de la table.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7792,7 +8274,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de après la sieste. Tom est rangé. Un chat miaule une fois. Sami range la tasse. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. Le bus rouge a glissé vers l'assiette. La nappe est un peu chaude. Raphaël est près de la table, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7932,10 +8414,30 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Un chat miaule une fois. Sami range la tasse. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Le bus rouge a glissé vers l'assiette.
+narrateur|La nappe est un peu chaude.
+narrateur|Raphaël est près de la table, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7960,7 +8462,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de la table. Il a joué avec le bus rouge, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8100,7 +8602,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de la table.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8128,7 +8639,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de le bus. Et de Tom. Et de le soir. Un ballon s'immobilise. J'ai appris. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. Le bus rouge attend près de la tasse. Ça sent la soupe. Raphaël est près de la table, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8268,12 +8779,30 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sami se souvient de le bus. Et de Tom. Et de le soir. Un ballon s'immobilise.
-enfant-m|J'ai appris. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci.
-narrateur|Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Le bus rouge attend près de la tasse.
+narrateur|Ça sent la soupe.
+narrateur|Raphaël est près de la table, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8298,7 +8827,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de la table. Il a joué avec le bus rouge, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8438,7 +8967,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de la table.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8466,7 +9004,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est après la sieste. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël va près de la fenêtre, avec le bus rouge. La vitre est un peu floue. Mila trace un petit rond du doigt. Bonjour, Mila. Bonjour. Tu veux le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Bravo, Raphaël. Merci. Je vois le marché. On dit les mots, même près de la fenêtre. Bonjour. S'il te plaît. Merci. Un oiseau passe derrière la vitre.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8606,10 +9144,30 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est après la sieste. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Raphaël va près de la fenêtre, avec le bus rouge.
+narrateur|La vitre est un peu floue.
+narrateur|Mila trace un petit rond du doigt.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux le torchon, pour la vitre ?
+enfant-m|S'il te plaît.
+narrateur|Le torchon est doux, un peu épais.
+enfant-m|Merci, papa.
+maman|Bravo, Raphaël.
+enfant-f|Merci.
+enfant-f|Je vois le marché.
+maman|On dit les mots, même près de la fenêtre.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Un oiseau passe derrière la vitre.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>vitre</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8634,7 +9192,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8798,7 +9356,8 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8826,7 +9385,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le bus. Sami s'arrête. On dit merci. Maman n'est pas loin. Sami les rejoint. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. Un vrai bus passe derrière la fenêtre. Le bus rouge le regarde, tout petit. Raphaël est près de la fenêtre, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8966,10 +9525,30 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le bus. Sami s'arrête. On dit merci. Maman n'est pas loin. Sami les rejoint. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|Un vrai bus passe derrière la fenêtre.
+narrateur|Le bus rouge le regarde, tout petit.
+narrateur|Raphaël est près de la fenêtre, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8994,7 +9573,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de la fenêtre. Il a joué avec le bus rouge, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9134,7 +9713,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de la fenêtre.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9162,7 +9750,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sami range Léa. après la sieste reste près de le bus. On se tient la main. Sami souffle, puis sourit à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. La vitre est tiède. Le bus rouge repose sur le rebord. Raphaël est près de la fenêtre, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9302,10 +9890,30 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sami range Léa. après la sieste reste près de le bus. On se tient la main. Sami souffle, puis sourit à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|La vitre est tiède.
+narrateur|Le bus rouge repose sur le rebord.
+narrateur|Raphaël est près de la fenêtre, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9330,7 +9938,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de la fenêtre. Il a joué avec le bus rouge, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9470,7 +10078,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de la fenêtre.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9498,7 +10115,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. Les lumières de la rue dansent sur la vitre. Le bus rouge est calme. Raphaël est près de la fenêtre, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9638,10 +10255,30 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le bus reste dans le souvenir. Un panier est posé sur le banc. Sami sourit. Papa sourit aussi. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Les lumières de la rue dansent sur la vitre.
+narrateur|Le bus rouge est calme.
+narrateur|Raphaël est près de la fenêtre, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9666,7 +10303,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de la fenêtre. Il a joué avec le bus rouge, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9806,7 +10443,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de la fenêtre.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9834,7 +10480,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le soir. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël glisse le bus rouge près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Bonjour, Mila. Bonjour. Tu veux le tabouret, Raphaël ? S'il te plaît. Tu peux. Merci. Raphaël pose une main sur le bois lisse. Bravo. Tu as demandé. Merci, Mila. Les trois mots, même pour un tabouret. Bonjour. S'il te plaît. Merci. Le tabouret fait un tout petit craquement.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9974,10 +10620,31 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à Léa. Il demande une place : s'il te plaît. Léa dit merci. C'est le soir. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Raphaël glisse le bus rouge près du tabouret.
+narrateur|Le tabouret est bas, en bois clair.
+narrateur|Mila s'assoit, les pieds qui balancent.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+maman|Tu veux le tabouret, Raphaël ?
+enfant-m|S'il te plaît.
+enfant-f|Tu peux.
+enfant-f|Merci.
+narrateur|Raphaël pose une main sur le bois lisse.
+papa|Bravo.
+papa|Tu as demandé.
+enfant-m|Merci, Mila.
+maman|Les trois mots, même pour un tabouret.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Le tabouret fait un tout petit craquement.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>bois</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10002,7 +10669,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10166,7 +10833,8 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10194,7 +10862,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Sami est rangé. le bus est fini. L'eau coule, tout petit bruit. Sami prend la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. Le bus rouge est sous le tabouret. Mila balance les pieds. Raphaël est près de le tabouret, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10334,10 +11002,30 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Sami est rangé. le bus est fini. L'eau coule, tout petit bruit. Sami prend la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|Le bus rouge est sous le tabouret.
+narrateur|Mila balance les pieds.
+narrateur|Raphaël est près de le tabouret, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10362,7 +11050,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de le tabouret. Il a joué avec le bus rouge, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10502,7 +11190,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de le tabouret.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10530,7 +11227,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sami pose Sami. le bus est derrière. Une pomme brille un peu. Sami caresse le doudou. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. Le tabouret a une ombre ronde. Le bus rouge sort tout doux. Raphaël est près de le tabouret, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10670,10 +11367,30 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Sami pose Sami. le bus est derrière. Une pomme brille un peu. Sami caresse le doudou. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Le tabouret a une ombre ronde.
+narrateur|Le bus rouge sort tout doux.
+narrateur|Raphaël est près de le tabouret, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10698,7 +11415,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de le tabouret. Il a joué avec le bus rouge, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10838,7 +11555,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de le tabouret.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10866,7 +11592,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sami montre le soir. Papa a vu le bus. Et Sami. Une tasse cliquette. Sami enfile ses chaussons. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. Le tabouret est près de la lampe. Le bus rouge rentre dans sa boîte. Raphaël est près de le tabouret, avec le bus rouge. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11006,10 +11732,30 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sami montre le soir. Papa a vu le bus. Et Sami. Une tasse cliquette. Sami enfile ses chaussons. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|Le tabouret est près de la lampe.
+narrateur|Le bus rouge rentre dans sa boîte.
+narrateur|Raphaël est près de le tabouret, avec le bus rouge.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11034,7 +11780,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de le tabouret. Il a joué avec le bus rouge, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11174,7 +11920,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de le tabouret.
+narrateur|Il a joué avec le bus rouge, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11202,7 +11957,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami entend une voiture. Un copain entre. Sami dit bonjour. Il demande une part : s'il te plaît. Il dit merci. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Dehors, une portière claque, tout loin. Mila arrive, son manteau sent la pluie. Bonjour, Mila. Bonjour, Raphaël. Bonjour. Donne-moi ton manteau. S'il te plaît. Merci, Mila. Tu veux une pomme, Raphaël ? S'il te plaît. La rondelle est froide et douce. Merci, papa. Bravo, les trois mots. Bonjour. S'il te plaît. Merci. La petite voiture brille près du bol.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11342,12 +12097,30 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sami entend une voiture. Un copain entre. Sami dit bonjour. Il demande une part : s'il te plaît. Il dit merci. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>narrateur|Raphaël prend la petite voiture.
+narrateur|Elle est lisse, un peu froide.
+narrateur|Dehors, une portière claque, tout loin.
+narrateur|Mila arrive, son manteau sent la pluie.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour, Raphaël.
+maman|Bonjour.
+maman|Donne-moi ton manteau.
+enfant-f|S'il te plaît.
+maman|Merci, Mila.
+papa|Tu veux une pomme, Raphaël ?
+enfant-m|S'il te plaît.
+narrateur|La rondelle est froide et douce.
+enfant-m|Merci, papa.
+maman|Bravo, les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|La petite voiture brille près du bol.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>voiture_passe</t>
+          <t>voiture_passe,porte</t>
         </is>
       </c>
     </row>
@@ -11562,7 +12335,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Bonjour, s'il te plaît, merci. Sami hoche la tête. On continue, avec papa. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Oui. On dit merci. Et bonjour. Et s'il te plaît. Raphaël hoche la tête. Bravo, Raphaël. Tu as fait du bon travail. Merci, maman.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11706,7 +12479,14 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Bonjour, s'il te plaît, merci. Sami hoche la tête. On continue, avec papa. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>narrateur|Oui.
+maman|On dit merci.
+papa|Et bonjour.
+papa|Et s'il te plaît.
+narrateur|Raphaël hoche la tête.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11734,7 +12514,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On va où, dans la cuisine ? La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11902,7 +12682,8 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On va où, dans la cuisine ?
+papa|La table, la fenêtre, ou le tabouret.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11930,7 +12711,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le matin. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël pose la petite voiture près de la table. Le bol jaune est au milieu. Mila tire une chaise, tout doux. Bonjour, Mila. Bonjour. Une assiette, Raphaël ? S'il te plaît. L'assiette est ronde, un peu froide. Merci, maman. Bravo. Tu as dit les mots. S'il te plaît. Une pomme. Voilà. Merci d'avoir demandé. Une rondelle brille dans l'assiette. Les mots gentils, à table aussi.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12070,10 +12851,30 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le matin. Papa reste tout près. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Raphaël pose la petite voiture près de la table.
+narrateur|Le bol jaune est au milieu.
+narrateur|Mila tire une chaise, tout doux.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+maman|Une assiette, Raphaël ?
+enfant-m|S'il te plaît.
+narrateur|L'assiette est ronde, un peu froide.
+enfant-m|Merci, maman.
+papa|Bravo.
+papa|Tu as dit les mots.
+enfant-f|S'il te plaît.
+enfant-f|Une pomme.
+papa|Voilà.
+papa|Merci d'avoir demandé.
+narrateur|Une rondelle brille dans l'assiette.
+maman|Les mots gentils, à table aussi.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>assiette</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12098,7 +12899,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12262,7 +13063,8 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12290,7 +13092,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sami a choisi la voiture. Puis Tom. Puis le matin. On range un objet. Sami répète tout bas le geste. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. La petite voiture roule vers le bol, sur la table. Une goutte d'eau brille sur le bois. Raphaël est près de la table, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12430,10 +13232,30 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sami a choisi la voiture. Puis Tom. Puis le matin. On range un objet. Sami répète tout bas le geste. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La petite voiture roule vers le bol, sur la table.
+narrateur|Une goutte d'eau brille sur le bois.
+narrateur|Raphaël est près de la table, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12458,7 +13280,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de la table. Il a joué avec la petite voiture, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12598,7 +13420,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de la table.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12626,7 +13457,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sami s'arrête près de après la sieste. Tom est rangé. Il y a des miettes sur la table. Sami pose sa tête un moment. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. La petite voiture dort près de l'assiette. Ça sent encore le pain. Raphaël est près de la table, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12766,10 +13597,30 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sami s'arrête près de après la sieste. Tom est rangé. Il y a des miettes sur la table. Sami pose sa tête un moment. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|La petite voiture dort près de l'assiette.
+narrateur|Ça sent encore le pain.
+narrateur|Raphaël est près de la table, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12794,7 +13645,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de la table. Il a joué avec la petite voiture, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12934,7 +13785,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de la table.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12962,7 +13822,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sami se souvient de la voiture. Et de Tom. Et de le soir. Un galet est encore chaud. Sami plie un pull. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. La petite voiture se gare près de la tasse. La table est tiède. Raphaël est près de la table, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13102,10 +13962,30 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sami se souvient de la voiture. Et de Tom. Et de le soir. Un galet est encore chaud. Sami plie un pull. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La petite voiture se gare près de la tasse.
+narrateur|La table est tiède.
+narrateur|Raphaël est près de la table, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13130,7 +14010,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de la table. Il a joué avec la petite voiture, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13270,7 +14150,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de la table.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13298,7 +14187,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est après la sieste. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël va près de la fenêtre, avec la petite voiture. La vitre est un peu floue. Mila trace un petit rond du doigt. Bonjour, Mila. Bonjour. Tu veux le torchon, pour la vitre ? S'il te plaît. Le torchon est doux, un peu épais. Merci, papa. Bravo, Raphaël. Merci. Je vois le marché. On dit les mots, même près de la fenêtre. Bonjour. S'il te plaît. Merci. Un oiseau passe derrière la vitre.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13438,10 +14327,30 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est après la sieste. Papa montre le geste, lentement. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Raphaël va près de la fenêtre, avec la petite voiture.
+narrateur|La vitre est un peu floue.
+narrateur|Mila trace un petit rond du doigt.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux le torchon, pour la vitre ?
+enfant-m|S'il te plaît.
+narrateur|Le torchon est doux, un peu épais.
+enfant-m|Merci, papa.
+maman|Bravo, Raphaël.
+enfant-f|Merci.
+enfant-f|Je vois le marché.
+maman|On dit les mots, même près de la fenêtre.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Un oiseau passe derrière la vitre.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>vitre</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13466,7 +14375,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13630,7 +14539,8 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13658,7 +14568,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de la voiture. Sami s'arrête. On attend son tour. Sami s'assoit près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. La petite voiture touche la vitre froide. Un oiseau crie une fois. Raphaël est près de la fenêtre, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13798,10 +14708,30 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de la voiture. Sami s'arrête. On attend son tour. Sami s'assoit près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La petite voiture touche la vitre froide.
+narrateur|Un oiseau crie une fois.
+narrateur|Raphaël est près de la fenêtre, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13826,7 +14756,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de la fenêtre. Il a joué avec la petite voiture, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13966,7 +14896,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de la fenêtre.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13994,7 +14933,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sami range Léa. après la sieste reste près de la voiture. La lumière est claire. Sami serre la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. La vitre a un petit nuage. La petite voiture attend sur le rebord. Raphaël est près de la fenêtre, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14134,10 +15073,30 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sami range Léa. après la sieste reste près de la voiture. La lumière est claire. Sami serre la main de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|La vitre a un petit nuage.
+narrateur|La petite voiture attend sur le rebord.
+narrateur|Raphaël est près de la fenêtre, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14162,7 +15121,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de la fenêtre. Il a joué avec la petite voiture, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14302,7 +15261,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de la fenêtre.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14330,7 +15298,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. La vitre est noire, un peu. La petite voiture brille sous la lampe. Raphaël est près de la fenêtre, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14470,10 +15438,30 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. la voiture reste dans le souvenir. La couverture est douce. Sami range encore un peu, près de papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La vitre est noire, un peu.
+narrateur|La petite voiture brille sous la lampe.
+narrateur|Raphaël est près de la fenêtre, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14498,7 +15486,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de la fenêtre. Il a joué avec la petite voiture, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14638,7 +15626,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de la fenêtre.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14666,7 +15663,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le soir. Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
+          <t>Raphaël glisse la petite voiture près du tabouret. Le tabouret est bas, en bois clair. Mila s'assoit, les pieds qui balancent. Bonjour, Mila. Bonjour. Tu veux le tabouret, Raphaël ? S'il te plaît. Tu peux. Merci. Raphaël pose une main sur le bois lisse. Bravo. Tu as demandé. Merci, Mila. Les trois mots, même pour un tabouret. Bonjour. S'il te plaît. Merci. Le tabouret fait un tout petit craquement.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14806,11 +15803,31 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sami dit bonjour à un copain Sami. Il dit s'il te plaît. Il dit merci. C'est le soir.
-papa|Je suis là. On dit bonjour. On dit s'il te plaît. On dit merci.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Raphaël glisse la petite voiture près du tabouret.
+narrateur|Le tabouret est bas, en bois clair.
+narrateur|Mila s'assoit, les pieds qui balancent.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+maman|Tu veux le tabouret, Raphaël ?
+enfant-m|S'il te plaît.
+enfant-f|Tu peux.
+enfant-f|Merci.
+narrateur|Raphaël pose une main sur le bois lisse.
+papa|Bravo.
+papa|Tu as demandé.
+enfant-m|Merci, Mila.
+maman|Les trois mots, même pour un tabouret.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+narrateur|Le tabouret fait un tout petit craquement.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>bois</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14835,7 +15852,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14999,7 +16016,8 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15027,7 +16045,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sami rejoint le matin. Sami est rangé. la voiture est fini. Le vent est doux. Sami ferme la porte, tout doux. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le matin. La petite voiture tourne autour du tabouret. Le bois est frais. Raphaël est près de le tabouret, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15167,10 +16185,30 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sami rejoint le matin. Sami est rangé. la voiture est fini. Le vent est doux. Sami ferme la porte, tout doux. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La petite voiture tourne autour du tabouret.
+narrateur|Le bois est frais.
+narrateur|Raphaël est près de le tabouret, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>matin</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15195,7 +16233,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, près de le tabouret. Il a joué avec la petite voiture, avec Mila. Le soleil a touché le bol jaune. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15335,7 +16373,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, près de le tabouret.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|Le soleil a touché le bol jaune.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15363,7 +16410,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Sami pose Sami. la voiture est derrière. Le sol est un peu froid. Sami montre après la sieste à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est après la sieste. Le tabouret a gardé le soleil. La petite voiture est tiède. Raphaël est près de le tabouret, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15503,10 +16550,30 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Sami pose Sami. la voiture est derrière. Le sol est un peu froid. Sami montre après la sieste à papa. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Le tabouret a gardé le soleil.
+narrateur|La petite voiture est tiède.
+narrateur|Raphaël est près de le tabouret, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>sieste</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15531,7 +16598,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, près de le tabouret. Il a joué avec la petite voiture, avec Mila. Le pain a senti bon, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15671,7 +16738,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, près de le tabouret.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|Le pain a senti bon, tout calme.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15699,7 +16775,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sami montre le soir. Papa a vu la voiture. Et Sami. On souffle doucement. Sami range la voiture dans sa tête, comme un souvenir. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
+          <t>C'est le soir. La petite voiture se range sous le tabouret. On entend la casserole, tout loin. Raphaël est près de le tabouret, avec la petite voiture. Bonjour, Mila. Bonjour. Tu veux encore une rondelle ? S'il te plaît. La pomme est froide, un peu sucrée. Merci, papa. Bravo. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Merci, Raphaël. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15839,10 +16915,30 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sami montre le soir. Papa a vu la voiture. Et Sami. On souffle doucement. Sami range la voiture dans sa tête, comme un souvenir. On dit bonjour. On dit s'il te plaît. On dit merci. On dit le mot : bonjour, s'il te plaît, ou merci. Sami dit merci à papa.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La petite voiture se range sous le tabouret.
+narrateur|On entend la casserole, tout loin.
+narrateur|Raphaël est près de le tabouret, avec la petite voiture.
+enfant-m|Bonjour, Mila.
+enfant-f|Bonjour.
+papa|Tu veux encore une rondelle ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est froide, un peu sucrée.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les trois mots.
+papa|Bonjour.
+papa|S'il te plaît.
+papa|Merci.
+enfant-f|Merci, Raphaël.
+maman|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>lampe</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15867,7 +16963,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, près de le tabouret. Il a joué avec la petite voiture, avec Mila. La lampe a fait un rond doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Raphaël. Tu as fait du bon travail. Bonne journée, mon grand. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16007,7 +17103,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, près de le tabouret.
+narrateur|Il a joué avec la petite voiture, avec Mila.
+narrateur|La lampe a fait un rond doux.
+maman|Tu as dit bonjour.
+papa|Tu as dit s'il te plaît.
+enfant-m|Et merci.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Bonne journée, mon grand.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16029,7 +17134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16081,6 +17186,13 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-001.xlsx
+++ b/stories/arbres/TREE-COL-001.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>dans la cuisine</t>
+          <t>cuisine, après le marché</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Raphaël, Mila, maman, papa</t>
+          <t>Raphaël, Mila, papa, maman</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Raphaël veut donner des pommes à Mila. Ils font le voyage des pommes avec un train, un bus ou une voiture, jusqu'à un arrêt. Ils poussent, ils livrent, ils croquent.</t>
+          <t>Raphaël veut livrer les pommes à Mila. Une pomme s'échappe. Ils la retrouvent, puis le voyage reprend.</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil se pose sur le carrelage. Papa a mis des rondelles dans un bol jaune. En ce moment, Raphaël tient une cuillère en bois. Je veux donner des pommes à Mila. On fait le voyage des pommes. Elle arrive tout à l'heure. Tu prends un véhicule, en attendant ?</t>
+          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil se pose sur le carrelage. Papa a mis des rondelles dans un bol jaune. Une pomme entière reste au bord, trop ronde. Je veux les porter jusqu'à Mila. Elle rentre du marché, tout à l'heure. Tu prends un véhicule, en attendant ? En ce moment, Raphaël touche le bol. Le bol est un peu lourd. On fait le voyage des pommes. Le train, le bus, ou la voiture ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil se pose sur le carrelage. Papa a mis des rondelles dans un bol jaune. En ce moment, Raphaël tient une cuillère en bois. Je veux donner des pommes à Mila. On fait le voyage des pommes. Elle arrive tout à l'heure. Tu prends un véhicule, en attendant ?</t>
+          <t>Une goutte glisse le long de la casserole. Ça sent la pomme, toute douce. Le torchon rayé pend près de l'évier. Dehors, le marché parle tout bas. Un rond de soleil se pose sur le carrelage. Papa a mis des rondelles dans un bol jaune. Une pomme entière reste au bord, trop ronde. Je veux les porter jusqu'à Mila. Elle rentre du marché, tout à l'heure. Tu prends un véhicule, en attendant ? En ce moment, Raphaël touche le bol. Le bol est un peu lourd. On fait le voyage des pommes. Le train, le bus, ou la voiture ?</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1338,16 +1338,19 @@
 narrateur|Dehors, le marché parle tout bas.
 narrateur|Un rond de soleil se pose sur le carrelage.
 narrateur|Papa a mis des rondelles dans un bol jaune.
-narrateur|En ce moment, Raphaël tient une cuillère en bois.
-enfant-m|Je veux donner des pommes à Mila.
+narrateur|Une pomme entière reste au bord, trop ronde.
+enfant-m|Je veux les porter jusqu'à Mila.
+maman|Elle rentre du marché, tout à l'heure.
+papa|Tu prends un véhicule, en attendant ?
+narrateur|En ce moment, Raphaël touche le bol.
+narrateur|Le bol est un peu lourd.
 enfant-m|On fait le voyage des pommes.
-maman|Elle arrive tout à l'heure.
-papa|Tu prends un véhicule, en attendant ?</t>
+papa|Le train, le bus, ou la voiture ?</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>casserole,pomme</t>
+          <t>goutte</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1377,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Qu'est-ce que Raphaël prend ? Le train, le bus, ou la voiture.</t>
+          <t>Trois jouets attendent près du bol. Le train, le bus, ou la voiture. Qu'est-ce que tu prends, Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Qu'est-ce que Raphaël prend ? Le train, le bus, ou la voiture.</t>
+          <t>Trois jouets attendent près du bol. Le train, le bus, ou la voiture. Qu'est-ce que tu prends, Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1463,14 +1466,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1538,8 +1541,9 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Qu'est-ce que Raphaël prend ?
-narrateur|Le train, le bus, ou la voiture.</t>
+          <t>narrateur|Trois jouets attendent près du bol.
+narrateur|Le train, le bus, ou la voiture.
+maman|Qu'est-ce que tu prends, Raphaël ?</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1570,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Le train s'arrête près de ses pieds. C'est le voyage des pommes. J'apporte le bol ? Il est un peu lourd. On le met sur le train. Ils glissent le bol jaune entre deux wagons. Merci. Il tient.</t>
+          <t>Raphaël prend le train. Les roues font clic, sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. C'est le train des pommes. J'apporte le bol ? Il est un peu lourd. S'il te plaît, aide-nous. Merci, Mila. Ils glissent le bol, tout doux. La pomme ronde tremble au bord. Elle tombe entre deux wagons. Elle est partie ! Le voyage attend.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le train en bois. Les roues font un petit clic sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. Le train s'arrête près de ses pieds. C'est le voyage des pommes. J'apporte le bol ? Il est un peu lourd. On le met sur le train. Ils glissent le bol jaune entre deux wagons. Merci. Il tient.</t>
+          <t>Raphaël prend le train. Les roues font clic, sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. C'est le train des pommes. J'apporte le bol ? Il est un peu lourd. S'il te plaît, aide-nous. Merci, Mila. Ils glissent le bol, tout doux. La pomme ronde tremble au bord. Elle tombe entre deux wagons. Elle est partie ! Le voyage attend.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1634,7 +1638,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1706,18 +1710,22 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël prend le train en bois.
-narrateur|Les roues font un petit clic sur le carrelage.
-narrateur|La porte s'ouvre. Mila entre, les joues roses.
+          <t>narrateur|Raphaël prend le train.
+narrateur|Les roues font clic, sur le carrelage.
+narrateur|La porte s'ouvre.
+narrateur|Mila entre, les joues roses.
 enfant-m|Bonjour, Mila.
 enfant-f|Bonjour, Raphaël.
-narrateur|Le train s'arrête près de ses pieds.
-enfant-m|C'est le voyage des pommes.
+enfant-m|C'est le train des pommes.
 enfant-f|J'apporte le bol ?
 papa|Il est un peu lourd.
-enfant-m|On le met sur le train.
-narrateur|Ils glissent le bol jaune entre deux wagons.
-enfant-f|Merci. Il tient.</t>
+enfant-m|S'il te plaît, aide-nous.
+papa|Merci, Mila.
+narrateur|Ils glissent le bol, tout doux.
+narrateur|La pomme ronde tremble au bord.
+narrateur|Elle tombe entre deux wagons.
+enfant-f|Elle est partie !
+enfant-m|Le voyage attend.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1749,27 +1757,27 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle allée ?</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle allée ?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Mila arrive. Raphaël dit quoi ?</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Mila arrive. Raphaël dit quoi ?</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Mila arrive. Raphaël dit quoi ?</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>bonjour</t>
+          <t>wagons</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>bonjour | bonjour mila</t>
+          <t>entre les wagons | pomme | par terre | le train</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1784,7 +1792,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>Il dit bonjour.</t>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle ?</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1833,7 +1841,7 @@
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1909,7 +1917,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Mila arrive. Raphaël dit quoi ?</t>
+          <t>narrateur|La pomme ronde n'est plus dans le bol.
+maman|Où est-elle allée ?</t>
         </is>
       </c>
     </row>
@@ -1936,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit bonjour. Le bol est sur le train. On cherche l'arrêt. Choisissez l'endroit.</t>
+          <t>Ils se baissent vers entre les wagons. La pomme brille encore, un peu loin. On la suit. Doucement, le carrelage est froid. Merci, papa. Le bol reste sur le véhicule.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit bonjour. Le bol est sur le train. On cherche l'arrêt. Choisissez l'endroit.</t>
+          <t>Ils se baissent vers entre les wagons. La pomme brille encore, un peu loin. On la suit. Doucement, le carrelage est froid. Merci, papa. Le bol reste sur le véhicule.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2004,7 +2013,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2080,10 +2089,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a dit bonjour.
-narrateur|Le bol est sur le train.
-enfant-m|On cherche l'arrêt.
-maman|Choisissez l'endroit.</t>
+          <t>narrateur|Ils se baissent vers entre les wagons.
+narrateur|La pomme brille encore, un peu loin.
+enfant-f|On la suit.
+papa|Doucement, le carrelage est froid.
+enfant-m|Merci, papa.
+narrateur|Le bol reste sur le véhicule.</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2121,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
+          <t>La pomme roule encore un peu. La table, la fenêtre, ou le tabouret. Elle va où, d'après toi ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
+          <t>La pomme roule encore un peu. La table, la fenêtre, ou le tabouret. Elle va où, d'après toi ?</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2199,14 +2210,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA7" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
@@ -2278,8 +2289,9 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|L'arrêt, c'est où ?
-narrateur|La table, la fenêtre, ou le tabouret.</t>
+          <t>narrateur|La pomme roule encore un peu.
+narrateur|La table, la fenêtre, ou le tabouret.
+papa|Elle va où, d'après toi ?</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2318,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ils poussent le train jusqu'à la table. Le bol jaune glisse un peu. Raphaël le rattrape. Arrêt table. On décharge ici. Mila tire une chaise. Raphaël pose deux assiettes. Vous avez besoin d'aide ? On fait le voyage.</t>
+          <t>La pomme file vers la table. Des miettes collent à la nappe. Elle s'arrête sous la nappe. Le train reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Ils poussent le train jusqu'à la table. Le bol jaune glisse un peu. Raphaël le rattrape. Arrêt table. On décharge ici. Mila tire une chaise. Raphaël pose deux assiettes. Vous avez besoin d'aide ? On fait le voyage.</t>
+          <t>La pomme file vers la table. Des miettes collent à la nappe. Elle s'arrête sous la nappe. Le train reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2374,7 +2386,7 @@
         <v>0.92</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
@@ -2446,13 +2458,13 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Ils poussent le train jusqu'à la table.
-narrateur|Le bol jaune glisse un peu. Raphaël le rattrape.
-enfant-m|Arrêt table.
-enfant-f|On décharge ici.
-narrateur|Mila tire une chaise. Raphaël pose deux assiettes.
-maman|Vous avez besoin d'aide ?
-enfant-m|On fait le voyage.</t>
+          <t>narrateur|La pomme file vers la table.
+narrateur|Des miettes collent à la nappe.
+narrateur|Elle s'arrête sous la nappe.
+narrateur|Le train reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -2484,12 +2496,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2512,7 +2524,7 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2522,7 +2534,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -2532,7 +2544,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -2573,14 +2585,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA9" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
@@ -2648,8 +2660,9 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous la nappe. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le train peut repartir.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous la nappe. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le train peut repartir.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2744,7 +2757,7 @@
         <v>0.92</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
@@ -2816,14 +2829,16 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse le train, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, sous la nappe.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|Le train peut repartir.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -2855,12 +2870,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un clic lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un clic lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2916,14 +2931,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA11" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
@@ -2995,11 +3010,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|Le train s'arrête contre le bol jaune.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le train s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un clic lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3046,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous la nappe. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le train reprend clic.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous la nappe. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le train reprend clic.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3094,7 +3114,7 @@
         <v>0.92</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
@@ -3166,15 +3186,16 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse le train. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste sous la nappe.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|Le train reprend clic.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
@@ -3206,12 +3227,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La table garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La table garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3267,14 +3288,14 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA13" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
@@ -3346,11 +3367,15 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|Le train s'arrête contre le bol jaune.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le train rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|La table garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3402,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous la nappe, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous la nappe, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3445,7 +3470,7 @@
         <v>0.92</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
@@ -3517,14 +3542,16 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent le train avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme sous la nappe, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
@@ -3556,12 +3583,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le train dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Le train s'arrête contre le bol jaune. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le train dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3617,14 +3644,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA15" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB15" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
@@ -3696,11 +3723,15 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|Le train s'arrête contre le bol jaune.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|Le train dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -3727,12 +3758,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le train va près de la fenêtre. La vitre est un peu floue. Je dessine l'arrêt, dans la buée. Mila trace un petit rond. J'essuie juste à côté. Le rond reste. Le marché apparaît autour du rond. Arrêt fenêtre.</t>
+          <t>La pomme file vers la fenêtre. Le soleil rend la vitre glissante. Elle s'arrête contre la vitre. Le train reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Le train va près de la fenêtre. La vitre est un peu floue. Je dessine l'arrêt, dans la buée. Mila trace un petit rond. J'essuie juste à côté. Le rond reste. Le marché apparaît autour du rond. Arrêt fenêtre.</t>
+          <t>La pomme file vers la fenêtre. Le soleil rend la vitre glissante. Elle s'arrête contre la vitre. Le train reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3795,7 +3826,7 @@
         <v>0.92</v>
       </c>
       <c r="AB16" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
@@ -3867,13 +3898,13 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Le train va près de la fenêtre.
-narrateur|La vitre est un peu floue.
-enfant-f|Je dessine l'arrêt, dans la buée.
-narrateur|Mila trace un petit rond.
-enfant-m|J'essuie juste à côté. Le rond reste.
-narrateur|Le marché apparaît autour du rond.
-enfant-m|Arrêt fenêtre.</t>
+          <t>narrateur|La pomme file vers la fenêtre.
+narrateur|Le soleil rend la vitre glissante.
+narrateur|Elle s'arrête contre la vitre.
+narrateur|Le train reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -3905,12 +3936,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3933,7 +3964,7 @@
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3943,7 +3974,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -3953,7 +3984,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -3994,14 +4025,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA17" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB17" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
@@ -4069,8 +4100,9 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -4097,12 +4129,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, contre la vitre. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le train peut repartir.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, contre la vitre. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le train peut repartir.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4165,7 +4197,7 @@
         <v>0.92</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
@@ -4237,14 +4269,16 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse le train, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, contre la vitre.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|Le train peut repartir.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -4276,12 +4310,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un clic lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un clic lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4337,14 +4371,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA19" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB19" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
@@ -4416,11 +4450,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|Le train rentre sous le rebord.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le train s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un clic lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -4447,12 +4486,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste contre la vitre. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le train reprend clic.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste contre la vitre. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le train reprend clic.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4515,7 +4554,7 @@
         <v>0.92</v>
       </c>
       <c r="AB20" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
@@ -4587,15 +4626,16 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse le train. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste contre la vitre.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|Le train reprend clic.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -4627,12 +4667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La fenêtre garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La fenêtre garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4688,14 +4728,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA21" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB21" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
@@ -4767,11 +4807,15 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|Le train rentre sous le rebord.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le train rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|La fenêtre garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4842,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme contre la vitre, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme contre la vitre, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4866,7 +4910,7 @@
         <v>0.92</v>
       </c>
       <c r="AB22" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
@@ -4938,14 +4982,16 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent le train avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme contre la vitre, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -4977,12 +5023,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le train dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Le train rentre sous le rebord. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le train dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5038,14 +5084,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA23" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB23" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
@@ -5117,11 +5163,15 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|Le train rentre sous le rebord.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|Le train dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -5148,12 +5198,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Le train glisse jusqu'au tabouret. Le tabouret est bas, en bois clair. Je m'assois. C'est la gare haute. Je peux après ? Oui. Quand le bol est arrivé. Raphaël pose le bol sur le bois, près d'elle. Le tabouret fait un petit craquement.</t>
+          <t>La pomme file vers le tabouret. Une chaussette cache un coin. Elle s'arrête sous le tabouret. Le train reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Le train glisse jusqu'au tabouret. Le tabouret est bas, en bois clair. Je m'assois. C'est la gare haute. Je peux après ? Oui. Quand le bol est arrivé. Raphaël pose le bol sur le bois, près d'elle. Le tabouret fait un petit craquement.</t>
+          <t>La pomme file vers le tabouret. Une chaussette cache un coin. Elle s'arrête sous le tabouret. Le train reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5216,7 +5266,7 @@
         <v>0.92</v>
       </c>
       <c r="AB24" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
@@ -5288,13 +5338,13 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Le train glisse jusqu'au tabouret.
-narrateur|Le tabouret est bas, en bois clair.
-enfant-f|Je m'assois. C'est la gare haute.
-enfant-m|Je peux après ?
-enfant-f|Oui. Quand le bol est arrivé.
-narrateur|Raphaël pose le bol sur le bois, près d'elle.
-narrateur|Le tabouret fait un petit craquement.</t>
+          <t>narrateur|La pomme file vers le tabouret.
+narrateur|Une chaussette cache un coin.
+narrateur|Elle s'arrête sous le tabouret.
+narrateur|Le train reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -5326,12 +5376,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5354,7 +5404,7 @@
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5364,7 +5414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -5374,7 +5424,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -5415,14 +5465,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA25" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB25" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
@@ -5490,8 +5540,9 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous le tabouret. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le train peut repartir.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le train, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous le tabouret. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le train peut repartir.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5586,7 +5637,7 @@
         <v>0.92</v>
       </c>
       <c r="AB26" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
@@ -5658,14 +5709,16 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse le train, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, sous le tabouret.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|Le train peut repartir.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -5697,12 +5750,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un clic lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un clic lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5758,14 +5811,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA27" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB27" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
@@ -5837,11 +5890,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|Le train dort sous le tabouret.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le train s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un clic lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5926,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous le tabouret. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le train reprend clic.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le train. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous le tabouret. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le train reprend clic.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -5936,7 +5994,7 @@
         <v>0.92</v>
       </c>
       <c r="AB28" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
@@ -6008,15 +6066,16 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse le train. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste sous le tabouret.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|Le train reprend clic.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -6048,12 +6107,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. Le tabouret garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le train rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. Le tabouret garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6109,14 +6168,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA29" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB29" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
@@ -6188,11 +6247,15 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|Le train dort sous le tabouret.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le train rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|Le tabouret garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -6219,12 +6282,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous le tabouret, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le train avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous le tabouret, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -6287,7 +6350,7 @@
         <v>0.92</v>
       </c>
       <c r="AB30" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
@@ -6359,14 +6422,16 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent le train avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme sous le tabouret, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|Le train fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -6398,12 +6463,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le train dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Le train dort sous le tabouret. Terminus, les pommes. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le train dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -6459,14 +6524,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA31" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB31" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
@@ -6538,11 +6603,15 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|Le train dort sous le tabouret.
-enfant-m|Terminus, les pommes.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|Le train dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6638,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte. Bonjour, Mila. Bonjour. Une miette colle au rebord du bol. Le torchon, s'il te plaît. Le voilà. Merci. Il essuie. Le bol est propre. Les pommes montent dans le bus. Ils posent deux rondelles sur les sièges.</t>
+          <t>Raphaël prend le bus. Les roues font stop, sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. C'est le bus des pommes. J'apporte le bol ? Il est un peu lourd. S'il te plaît, aide-nous. Merci, Mila. Ils glissent le bol, tout doux. La pomme ronde tremble au bord. Elle roule sous la chaise. Elle est partie ! Le voyage attend.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend le bus rouge. Dehors, un vrai bus passe, tout bas. Mila pousse la porte. Bonjour, Mila. Bonjour. Une miette colle au rebord du bol. Le torchon, s'il te plaît. Le voilà. Merci. Il essuie. Le bol est propre. Les pommes montent dans le bus. Ils posent deux rondelles sur les sièges.</t>
+          <t>Raphaël prend le bus. Les roues font stop, sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. C'est le bus des pommes. J'apporte le bol ? Il est un peu lourd. S'il te plaît, aide-nous. Merci, Mila. Ils glissent le bol, tout doux. La pomme ronde tremble au bord. Elle roule sous la chaise. Elle est partie ! Le voyage attend.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6637,7 +6706,7 @@
         <v>0.92</v>
       </c>
       <c r="AB32" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
@@ -6709,18 +6778,22 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël prend le bus rouge.
-narrateur|Dehors, un vrai bus passe, tout bas.
-narrateur|Mila pousse la porte.
+          <t>narrateur|Raphaël prend le bus.
+narrateur|Les roues font stop, sur le carrelage.
+narrateur|La porte s'ouvre.
+narrateur|Mila entre, les joues roses.
 enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-narrateur|Une miette colle au rebord du bol.
-enfant-m|Le torchon, s'il te plaît.
-maman|Le voilà.
-enfant-m|Merci.
-narrateur|Il essuie. Le bol est propre.
-enfant-f|Les pommes montent dans le bus.
-narrateur|Ils posent deux rondelles sur les sièges.</t>
+enfant-f|Bonjour, Raphaël.
+enfant-m|C'est le bus des pommes.
+enfant-f|J'apporte le bol ?
+papa|Il est un peu lourd.
+enfant-m|S'il te plaît, aide-nous.
+papa|Merci, Mila.
+narrateur|Ils glissent le bol, tout doux.
+narrateur|La pomme ronde tremble au bord.
+narrateur|Elle roule sous la chaise.
+enfant-f|Elle est partie !
+enfant-m|Le voyage attend.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
@@ -6752,27 +6825,27 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle allée ?</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle allée ?</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
           <t>Raphaël veut le torchon. Que dit-il ?</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Raphaël veut le torchon. Que dit-il ?</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Raphaël veut le torchon. Que dit-il ?</t>
-        </is>
-      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>s'il te plaît</t>
+          <t>chaise</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>s'il te plaît | sil te plait</t>
+          <t>sous la chaise | pomme | par terre | le bus</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -6787,7 +6860,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>Il dit s'il te plaît.</t>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle ?</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
@@ -6836,7 +6909,7 @@
         <v>0.86</v>
       </c>
       <c r="AB33" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
@@ -6908,7 +6981,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël veut le torchon. Que dit-il ?</t>
+          <t>narrateur|La pomme ronde n'est plus dans le bol.
+maman|Où est-elle allée ?</t>
         </is>
       </c>
     </row>
@@ -6935,12 +7009,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit s'il te plaît. Le torchon a servi. Le bus est chargé. On cherche l'arrêt.</t>
+          <t>Ils se baissent vers sous la chaise. La pomme brille encore, un peu loin. On la suit. Doucement, le carrelage est froid. Merci, papa. Le bol reste sur le véhicule.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit s'il te plaît. Le torchon a servi. Le bus est chargé. On cherche l'arrêt.</t>
+          <t>Ils se baissent vers sous la chaise. La pomme brille encore, un peu loin. On la suit. Doucement, le carrelage est froid. Merci, papa. Le bol reste sur le véhicule.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -7003,7 +7077,7 @@
         <v>0.92</v>
       </c>
       <c r="AB34" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
@@ -7079,9 +7153,12 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a dit s'il te plaît.
-narrateur|Le torchon a servi. Le bus est chargé.
-enfant-f|On cherche l'arrêt.</t>
+          <t>narrateur|Ils se baissent vers sous la chaise.
+narrateur|La pomme brille encore, un peu loin.
+enfant-f|On la suit.
+papa|Doucement, le carrelage est froid.
+enfant-m|Merci, papa.
+narrateur|Le bol reste sur le véhicule.</t>
         </is>
       </c>
     </row>
@@ -7108,12 +7185,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
+          <t>La pomme roule encore un peu. La table, la fenêtre, ou le tabouret. Elle va où, d'après toi ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
+          <t>La pomme roule encore un peu. La table, la fenêtre, ou le tabouret. Elle va où, d'après toi ?</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -7197,14 +7274,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA35" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB35" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
@@ -7276,8 +7353,9 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|L'arrêt, c'est où ?
-narrateur|La table, la fenêtre, ou le tabouret.</t>
+          <t>narrateur|La pomme roule encore un peu.
+narrateur|La table, la fenêtre, ou le tabouret.
+papa|Elle va où, d'après toi ?</t>
         </is>
       </c>
     </row>
@@ -7304,12 +7382,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Le bus rouge arrive contre la table. Arrêt table. Portes. Mila ouvre la petite porte. Les rondelles descendent. Raphaël pose une assiette. Mila l'autre. Ticket pomme.</t>
+          <t>La pomme file vers la table. Des miettes collent à la nappe. Elle s'arrête sous la nappe. Le bus reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Le bus rouge arrive contre la table. Arrêt table. Portes. Mila ouvre la petite porte. Les rondelles descendent. Raphaël pose une assiette. Mila l'autre. Ticket pomme.</t>
+          <t>La pomme file vers la table. Des miettes collent à la nappe. Elle s'arrête sous la nappe. Le bus reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -7372,7 +7450,7 @@
         <v>0.92</v>
       </c>
       <c r="AB36" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
@@ -7444,11 +7522,13 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Le bus rouge arrive contre la table.
-enfant-m|Arrêt table. Portes.
-narrateur|Mila ouvre la petite porte. Les rondelles descendent.
-narrateur|Raphaël pose une assiette. Mila l'autre.
-enfant-f|Ticket pomme.</t>
+          <t>narrateur|La pomme file vers la table.
+narrateur|Des miettes collent à la nappe.
+narrateur|Elle s'arrête sous la nappe.
+narrateur|Le bus reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -7480,12 +7560,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -7508,7 +7588,7 @@
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7518,7 +7598,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -7528,7 +7608,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -7569,14 +7649,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA37" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB37" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
@@ -7644,8 +7724,9 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7753,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous la nappe. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le bus peut repartir.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous la nappe. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le bus peut repartir.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -7740,7 +7821,7 @@
         <v>0.92</v>
       </c>
       <c r="AB38" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
@@ -7812,14 +7893,16 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse le bus, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, sous la nappe.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|Le bus peut repartir.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -7851,12 +7934,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un stop lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un stop lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -7912,14 +7995,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA39" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB39" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
@@ -7991,11 +8074,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|Le bus reste collé à l'assiette.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le bus s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un stop lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -8022,12 +8110,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous la nappe. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le bus reprend stop.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous la nappe. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le bus reprend stop.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -8090,7 +8178,7 @@
         <v>0.92</v>
       </c>
       <c r="AB40" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
@@ -8162,15 +8250,16 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse le bus. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste sous la nappe.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|Le bus reprend stop.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -8202,12 +8291,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La table garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La table garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -8263,14 +8352,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA41" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB41" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
@@ -8342,11 +8431,15 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|Le bus reste collé à l'assiette.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le bus rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|La table garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -8373,12 +8466,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous la nappe, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous la nappe, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -8441,7 +8534,7 @@
         <v>0.92</v>
       </c>
       <c r="AB42" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
@@ -8513,14 +8606,16 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent le bus avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme sous la nappe, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -8552,12 +8647,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le bus dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Le bus reste collé à l'assiette. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le bus dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -8613,14 +8708,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA43" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB43" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
@@ -8692,11 +8787,15 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|Le bus reste collé à l'assiette.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|Le bus dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8822,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Le bus va près de la fenêtre. Un vrai bus passe dans la rue. On suit le grand. Mila essuie un coin. Raphaël garde un trait de buée. C'est notre ligne. Arrêt fenêtre.</t>
+          <t>La pomme file vers la fenêtre. Le soleil rend la vitre glissante. Elle s'arrête contre la vitre. Le bus reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Le bus va près de la fenêtre. Un vrai bus passe dans la rue. On suit le grand. Mila essuie un coin. Raphaël garde un trait de buée. C'est notre ligne. Arrêt fenêtre.</t>
+          <t>La pomme file vers la fenêtre. Le soleil rend la vitre glissante. Elle s'arrête contre la vitre. Le bus reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -8791,7 +8890,7 @@
         <v>0.92</v>
       </c>
       <c r="AB44" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
@@ -8863,12 +8962,13 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Le bus va près de la fenêtre.
-narrateur|Un vrai bus passe dans la rue.
-enfant-m|On suit le grand.
-narrateur|Mila essuie un coin. Raphaël garde un trait de buée.
-enfant-f|C'est notre ligne.
-enfant-m|Arrêt fenêtre.</t>
+          <t>narrateur|La pomme file vers la fenêtre.
+narrateur|Le soleil rend la vitre glissante.
+narrateur|Elle s'arrête contre la vitre.
+narrateur|Le bus reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
@@ -8900,12 +9000,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -8928,7 +9028,7 @@
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -8938,7 +9038,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -8948,7 +9048,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -8989,14 +9089,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA45" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB45" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
@@ -9064,8 +9164,9 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9193,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, contre la vitre. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le bus peut repartir.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, contre la vitre. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le bus peut repartir.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -9160,7 +9261,7 @@
         <v>0.92</v>
       </c>
       <c r="AB46" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
@@ -9232,14 +9333,16 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse le bus, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, contre la vitre.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|Le bus peut repartir.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -9271,12 +9374,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un stop lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un stop lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9332,14 +9435,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA47" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB47" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
@@ -9411,11 +9514,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|Le petit bus s'endort contre la vitre.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le bus s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un stop lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -9442,12 +9550,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste contre la vitre. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le bus reprend stop.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste contre la vitre. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le bus reprend stop.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -9510,7 +9618,7 @@
         <v>0.92</v>
       </c>
       <c r="AB48" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
@@ -9582,15 +9690,16 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse le bus. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste contre la vitre.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|Le bus reprend stop.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -9622,12 +9731,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La fenêtre garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La fenêtre garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -9683,14 +9792,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA49" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB49" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
@@ -9762,11 +9871,15 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|Le petit bus s'endort contre la vitre.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le bus rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|La fenêtre garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -9793,12 +9906,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme contre la vitre, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme contre la vitre, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -9861,7 +9974,7 @@
         <v>0.92</v>
       </c>
       <c r="AB50" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
@@ -9933,14 +10046,16 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent le bus avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme contre la vitre, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
@@ -9972,12 +10087,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le bus dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Le petit bus s'endort contre la vitre. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le bus dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -10033,14 +10148,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA51" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB51" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
@@ -10112,11 +10227,15 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|Le petit bus s'endort contre la vitre.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|Le bus dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -10143,12 +10262,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Le bus s'arrête au pied du tabouret. Arrêt tabouret. On monte la cargaison. Mila s'assoit. Les pieds balancent. Raphaël hisse le bol à côté d'elle. Gare haute. Les pommes voient tout.</t>
+          <t>La pomme file vers le tabouret. Une chaussette cache un coin. Elle s'arrête sous le tabouret. Le bus reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Le bus s'arrête au pied du tabouret. Arrêt tabouret. On monte la cargaison. Mila s'assoit. Les pieds balancent. Raphaël hisse le bol à côté d'elle. Gare haute. Les pommes voient tout.</t>
+          <t>La pomme file vers le tabouret. Une chaussette cache un coin. Elle s'arrête sous le tabouret. Le bus reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -10211,7 +10330,7 @@
         <v>0.92</v>
       </c>
       <c r="AB52" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
@@ -10283,11 +10402,13 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Le bus s'arrête au pied du tabouret.
-enfant-m|Arrêt tabouret. On monte la cargaison.
-narrateur|Mila s'assoit. Les pieds balancent.
-narrateur|Raphaël hisse le bol à côté d'elle.
-enfant-f|Gare haute. Les pommes voient tout.</t>
+          <t>narrateur|La pomme file vers le tabouret.
+narrateur|Une chaussette cache un coin.
+narrateur|Elle s'arrête sous le tabouret.
+narrateur|Le bus reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
@@ -10319,12 +10440,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -10347,7 +10468,7 @@
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -10357,7 +10478,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -10367,7 +10488,7 @@
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -10408,14 +10529,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA53" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB53" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
@@ -10483,8 +10604,9 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -10511,12 +10633,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous le tabouret. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le bus peut repartir.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse le bus, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous le tabouret. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. Le bus peut repartir.</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -10579,7 +10701,7 @@
         <v>0.92</v>
       </c>
       <c r="AB54" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
@@ -10651,14 +10773,16 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse le bus, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, sous le tabouret.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|Le bus peut repartir.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -10690,12 +10814,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un stop lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un stop lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -10751,14 +10875,14 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA55" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB55" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
@@ -10830,11 +10954,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|Le bus dort sous le tabouret.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le bus s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un stop lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10990,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous le tabouret. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le bus reprend stop.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse le bus. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous le tabouret. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. Le bus reprend stop.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -10929,7 +11058,7 @@
         <v>0.92</v>
       </c>
       <c r="AB56" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
@@ -11001,15 +11130,16 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse le bus. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste sous le tabouret.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|Le bus reprend stop.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -11041,12 +11171,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. Le tabouret garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>Le bus rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. Le tabouret garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -11102,14 +11232,14 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA57" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB57" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
@@ -11181,11 +11311,15 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|Le bus dort sous le tabouret.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le bus rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|Le tabouret garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11346,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous le tabouret, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent le bus avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous le tabouret, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -11280,7 +11414,7 @@
         <v>0.92</v>
       </c>
       <c r="AB58" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
@@ -11352,14 +11486,16 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent le bus avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme sous le tabouret, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|Le bus fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
@@ -11391,12 +11527,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le bus dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Le bus dort sous le tabouret. Ticket utilisé. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. Le bus dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -11452,14 +11588,14 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA59" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB59" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
@@ -11531,11 +11667,15 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|Le bus dort sous le tabouret.
-enfant-f|Ticket utilisé.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|Le bus dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -11562,12 +11702,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Mila arrive. Son manteau sent la pluie. Bonjour, Mila. Bonjour. Tu accroches mon manteau, s'il te plaît ? Oui. Maman accroche le manteau. Merci. Une rondelle pour la route ? Oui, merci. Il pose la rondelle sur le capot, pour de faux. Cargaison prête.</t>
+          <t>Raphaël prend la voiture. Les roues font toc, sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. C'est la voiture des pommes. J'apporte le bol ? Il est un peu lourd. S'il te plaît, aide-nous. Merci, Mila. Ils glissent le bol, tout doux. La pomme ronde tremble au bord. Elle se coince contre le livre. Elle est partie ! Le voyage attend.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Raphaël prend la petite voiture. Elle est lisse, un peu froide. Mila arrive. Son manteau sent la pluie. Bonjour, Mila. Bonjour. Tu accroches mon manteau, s'il te plaît ? Oui. Maman accroche le manteau. Merci. Une rondelle pour la route ? Oui, merci. Il pose la rondelle sur le capot, pour de faux. Cargaison prête.</t>
+          <t>Raphaël prend la voiture. Les roues font toc, sur le carrelage. La porte s'ouvre. Mila entre, les joues roses. Bonjour, Mila. Bonjour, Raphaël. C'est la voiture des pommes. J'apporte le bol ? Il est un peu lourd. S'il te plaît, aide-nous. Merci, Mila. Ils glissent le bol, tout doux. La pomme ronde tremble au bord. Elle se coince contre le livre. Elle est partie ! Le voyage attend.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -11630,7 +11770,7 @@
         <v>0.92</v>
       </c>
       <c r="AB60" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
@@ -11702,19 +11842,22 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël prend la petite voiture.
-narrateur|Elle est lisse, un peu froide.
-narrateur|Mila arrive. Son manteau sent la pluie.
+          <t>narrateur|Raphaël prend la voiture.
+narrateur|Les roues font toc, sur le carrelage.
+narrateur|La porte s'ouvre.
+narrateur|Mila entre, les joues roses.
 enfant-m|Bonjour, Mila.
-enfant-f|Bonjour.
-enfant-f|Tu accroches mon manteau, s'il te plaît ?
-maman|Oui.
-narrateur|Maman accroche le manteau.
-enfant-f|Merci.
-papa|Une rondelle pour la route ?
-enfant-m|Oui, merci.
-narrateur|Il pose la rondelle sur le capot, pour de faux.
-enfant-m|Cargaison prête.</t>
+enfant-f|Bonjour, Raphaël.
+enfant-m|C'est la voiture des pommes.
+enfant-f|J'apporte le bol ?
+papa|Il est un peu lourd.
+enfant-m|S'il te plaît, aide-nous.
+papa|Merci, Mila.
+narrateur|Ils glissent le bol, tout doux.
+narrateur|La pomme ronde tremble au bord.
+narrateur|Elle se coince contre le livre.
+enfant-f|Elle est partie !
+enfant-m|Le voyage attend.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
@@ -11746,27 +11889,27 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle allée ?</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle allée ?</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
           <t>Papa donne une rondelle. Que dit Raphaël ?</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Papa donne une rondelle. Que dit Raphaël ?</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Papa donne une rondelle. Que dit Raphaël ?</t>
-        </is>
-      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>merci</t>
+          <t>livre</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>merci | merci papa | oui merci</t>
+          <t>contre le livre | pomme | par terre | la voiture</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -11781,7 +11924,7 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Il dit merci.</t>
+          <t>La pomme ronde n'est plus dans le bol. Où est-elle ?</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr"/>
@@ -11830,7 +11973,7 @@
         <v>0.86</v>
       </c>
       <c r="AB61" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
@@ -11906,7 +12049,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Papa donne une rondelle. Que dit Raphaël ?</t>
+          <t>narrateur|La pomme ronde n'est plus dans le bol.
+maman|Où est-elle allée ?</t>
         </is>
       </c>
     </row>
@@ -11933,12 +12077,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit merci. La voiture a sa cargaison. On cherche l'arrêt.</t>
+          <t>Ils se baissent vers contre le livre. La pomme brille encore, un peu loin. On la suit. Doucement, le carrelage est froid. Merci, papa. Le bol reste sur le véhicule.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a dit merci. La voiture a sa cargaison. On cherche l'arrêt.</t>
+          <t>Ils se baissent vers contre le livre. La pomme brille encore, un peu loin. On la suit. Doucement, le carrelage est froid. Merci, papa. Le bol reste sur le véhicule.</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -12001,7 +12145,7 @@
         <v>0.92</v>
       </c>
       <c r="AB62" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
@@ -12077,9 +12221,12 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a dit merci.
-narrateur|La voiture a sa cargaison.
-enfant-m|On cherche l'arrêt.</t>
+          <t>narrateur|Ils se baissent vers contre le livre.
+narrateur|La pomme brille encore, un peu loin.
+enfant-f|On la suit.
+papa|Doucement, le carrelage est froid.
+enfant-m|Merci, papa.
+narrateur|Le bol reste sur le véhicule.</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12253,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
+          <t>La pomme roule encore un peu. La table, la fenêtre, ou le tabouret. Elle va où, d'après toi ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>L'arrêt, c'est où ? La table, la fenêtre, ou le tabouret.</t>
+          <t>La pomme roule encore un peu. La table, la fenêtre, ou le tabouret. Elle va où, d'après toi ?</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -12195,14 +12342,14 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA63" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB63" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
@@ -12274,8 +12421,9 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|L'arrêt, c'est où ?
-narrateur|La table, la fenêtre, ou le tabouret.</t>
+          <t>narrateur|La pomme roule encore un peu.
+narrateur|La table, la fenêtre, ou le tabouret.
+papa|Elle va où, d'après toi ?</t>
         </is>
       </c>
     </row>
@@ -12302,12 +12450,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>La voiture tourne autour de la table. Une goutte du manteau a séché. Parking table. Ils glissent la rondelle du capot dans une assiette. Livraison faite. Presque.</t>
+          <t>La pomme file vers la table. Des miettes collent à la nappe. Elle s'arrête sous la nappe. La voiture reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>La voiture tourne autour de la table. Une goutte du manteau a séché. Parking table. Ils glissent la rondelle du capot dans une assiette. Livraison faite. Presque.</t>
+          <t>La pomme file vers la table. Des miettes collent à la nappe. Elle s'arrête sous la nappe. La voiture reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -12370,7 +12518,7 @@
         <v>0.92</v>
       </c>
       <c r="AB64" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
@@ -12442,11 +12590,13 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|La voiture tourne autour de la table.
-narrateur|Une goutte du manteau a séché.
-enfant-m|Parking table.
-narrateur|Ils glissent la rondelle du capot dans une assiette.
-enfant-f|Livraison faite. Presque.</t>
+          <t>narrateur|La pomme file vers la table.
+narrateur|Des miettes collent à la nappe.
+narrateur|Elle s'arrête sous la nappe.
+narrateur|La voiture reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
@@ -12478,12 +12628,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -12506,7 +12656,7 @@
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -12516,7 +12666,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -12526,7 +12676,7 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -12567,14 +12717,14 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA65" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB65" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
@@ -12642,8 +12792,9 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -12670,12 +12821,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous la nappe. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. La voiture peut repartir.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous la nappe. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. La voiture peut repartir.</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -12738,7 +12889,7 @@
         <v>0.92</v>
       </c>
       <c r="AB66" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
@@ -12810,14 +12961,16 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse la voiture, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, sous la nappe.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|La voiture peut repartir.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -12849,12 +13002,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un toc lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un toc lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -12910,14 +13063,14 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA67" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB67" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
@@ -12989,11 +13142,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|La voiture se gare contre le bol.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|La voiture s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un toc lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13178,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous la nappe. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. La voiture reprend toc.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous la nappe. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. La voiture reprend toc.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13088,7 +13246,7 @@
         <v>0.92</v>
       </c>
       <c r="AB68" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
@@ -13160,15 +13318,16 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse la voiture. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste sous la nappe.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|La voiture reprend toc.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
@@ -13200,12 +13359,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La table garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La table garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -13261,14 +13420,14 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA69" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB69" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
@@ -13340,11 +13499,15 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|La voiture se gare contre le bol.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|La voiture rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|La table garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -13371,12 +13534,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous la nappe, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous la nappe, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -13439,7 +13602,7 @@
         <v>0.92</v>
       </c>
       <c r="AB70" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
@@ -13511,14 +13674,16 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent la voiture avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme sous la nappe, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
@@ -13550,12 +13715,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. La voiture dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>La voiture se gare contre le bol. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. La voiture dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -13611,14 +13776,14 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA71" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB71" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
@@ -13690,11 +13855,15 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|La voiture se gare contre le bol.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|La voiture dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -13721,12 +13890,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>La voiture va près de la fenêtre. Mila dessine une route dans la buée. J'essuie le bas. La route du haut reste. La petite voiture suit le trait. Arrêt fenêtre.</t>
+          <t>La pomme file vers la fenêtre. Le soleil rend la vitre glissante. Elle s'arrête contre la vitre. La voiture reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>La voiture va près de la fenêtre. Mila dessine une route dans la buée. J'essuie le bas. La route du haut reste. La petite voiture suit le trait. Arrêt fenêtre.</t>
+          <t>La pomme file vers la fenêtre. Le soleil rend la vitre glissante. Elle s'arrête contre la vitre. La voiture reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -13789,7 +13958,7 @@
         <v>0.92</v>
       </c>
       <c r="AB72" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
@@ -13861,11 +14030,13 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|La voiture va près de la fenêtre.
-narrateur|Mila dessine une route dans la buée.
-enfant-m|J'essuie le bas. La route du haut reste.
-narrateur|La petite voiture suit le trait.
-enfant-f|Arrêt fenêtre.</t>
+          <t>narrateur|La pomme file vers la fenêtre.
+narrateur|Le soleil rend la vitre glissante.
+narrateur|Elle s'arrête contre la vitre.
+narrateur|La voiture reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
@@ -13897,12 +14068,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -13925,7 +14096,7 @@
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -13935,7 +14106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -13945,7 +14116,7 @@
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -13986,14 +14157,14 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA73" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB73" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
@@ -14061,8 +14232,9 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -14089,12 +14261,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, contre la vitre. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. La voiture peut repartir.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, contre la vitre. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. La voiture peut repartir.</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -14157,7 +14329,7 @@
         <v>0.92</v>
       </c>
       <c r="AB74" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
@@ -14229,14 +14401,16 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse la voiture, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, contre la vitre.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|La voiture peut repartir.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -14268,12 +14442,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un toc lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un toc lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -14329,14 +14503,14 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA75" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB75" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
@@ -14408,11 +14582,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|La voiture s'arrête au bas de la vitre.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|La voiture s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un toc lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -14439,12 +14618,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste contre la vitre. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. La voiture reprend toc.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste contre la vitre. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. La voiture reprend toc.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -14507,7 +14686,7 @@
         <v>0.92</v>
       </c>
       <c r="AB76" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
@@ -14579,15 +14758,16 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse la voiture. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste contre la vitre.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|La voiture reprend toc.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
@@ -14619,12 +14799,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La fenêtre garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. La fenêtre garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -14680,14 +14860,14 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA77" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB77" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
@@ -14759,11 +14939,15 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|La voiture s'arrête au bas de la vitre.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|La voiture rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|La fenêtre garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -14790,12 +14974,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme contre la vitre, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme contre la vitre, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -14858,7 +15042,7 @@
         <v>0.92</v>
       </c>
       <c r="AB78" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
@@ -14930,14 +15114,16 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent la voiture avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme contre la vitre, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
@@ -14969,12 +15155,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. La voiture dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>La voiture s'arrête au bas de la vitre. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. La voiture dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -15030,14 +15216,14 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA79" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB79" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
@@ -15109,11 +15295,15 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|La voiture s'arrête au bas de la vitre.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|La voiture dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -15140,12 +15330,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La voiture arrive au tabouret. Je monte la voiture, tout doux ? Oui. Sur le bois. Il pose la voiture près d'elle. Le bol suit. Parking haut.</t>
+          <t>La pomme file vers le tabouret. Une chaussette cache un coin. Elle s'arrête sous le tabouret. La voiture reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>La voiture arrive au tabouret. Je monte la voiture, tout doux ? Oui. Sur le bois. Il pose la voiture près d'elle. Le bol suit. Parking haut.</t>
+          <t>La pomme file vers le tabouret. Une chaussette cache un coin. Elle s'arrête sous le tabouret. La voiture reste au milieu. On la voit à peine. Elle nous attend. Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -15208,7 +15398,7 @@
         <v>0.92</v>
       </c>
       <c r="AB80" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
@@ -15280,11 +15470,13 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|La voiture arrive au tabouret.
-enfant-m|Je monte la voiture, tout doux ?
-enfant-f|Oui. Sur le bois.
-narrateur|Il pose la voiture près d'elle. Le bol suit.
-enfant-f|Parking haut.</t>
+          <t>narrateur|La pomme file vers le tabouret.
+narrateur|Une chaussette cache un coin.
+narrateur|Elle s'arrête sous le tabouret.
+narrateur|La voiture reste au milieu.
+enfant-f|On la voit à peine.
+enfant-m|Elle nous attend.
+maman|Vous la prenez comment ?</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
@@ -15316,12 +15508,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Qui pousse pour livrer ? Mila, Raphaël, ou tous les deux.</t>
+          <t>La pomme ne bouge plus. On ramasse, on attend, ou on invente. Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -15344,7 +15536,7 @@
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>on ramasse</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -15354,7 +15546,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Raphaël</t>
+          <t>on attend</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -15364,7 +15556,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>tous les deux</t>
+          <t>on invente</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
@@ -15405,14 +15597,14 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA81" s="2" t="n">
         <v>0.87</v>
       </c>
       <c r="AB81" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
@@ -15480,8 +15672,9 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|Qui pousse pour livrer ?
-narrateur|Mila, Raphaël, ou tous les deux.</t>
+          <t>narrateur|La pomme ne bouge plus.
+narrateur|On ramasse, on attend, ou on invente.
+papa|Vous faites quoi, tous les deux ?</t>
         </is>
       </c>
     </row>
@@ -15508,12 +15701,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous le tabouret. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. La voiture peut repartir.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je garde les pommes. Mila pousse la voiture, tout autour de l'arrêt. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>S'il te plaît, le torchon. Le voilà. Mila tient le torchon. Raphaël glisse la main. Il touche la pomme, sous le tabouret. Je te la passe. Merci. La pomme est un peu froide. Ils la posent dans le bol. La voiture peut repartir.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -15576,7 +15769,7 @@
         <v>0.92</v>
       </c>
       <c r="AB82" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
@@ -15648,14 +15841,16 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>enfant-f|Je pousse.
-enfant-m|Moi, je garde les pommes.
-narrateur|Mila pousse la voiture, tout autour de l'arrêt.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|S'il te plaît, le torchon.
+maman|Le voilà.
+narrateur|Mila tient le torchon.
+narrateur|Raphaël glisse la main.
+narrateur|Il touche la pomme, sous le tabouret.
+enfant-f|Je te la passe.
+enfant-m|Merci.
+narrateur|La pomme est un peu froide.
+narrateur|Ils la posent dans le bol.
+narrateur|La voiture peut repartir.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
@@ -15687,12 +15882,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un toc lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture s'arrête près des assiettes. Terminus. Ils posent une rondelle chacun. La pomme sauvée reste au milieu. Celle-là a voyagé plus loin. Vous l'avez cherchée. Le torchon sent encore la pomme. Un toc lointain, sous la table. Il ne reste plus rien dans le bol. La casserole fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -15748,14 +15943,14 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA83" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB83" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
@@ -15827,11 +16022,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|La voiture descend du tabouret.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|La voiture s'arrête près des assiettes.
+enfant-m|Terminus.
+narrateur|Ils posent une rondelle chacun.
+narrateur|La pomme sauvée reste au milieu.
+enfant-f|Celle-là a voyagé plus loin.
+papa|Vous l'avez cherchée.
+maman|Le torchon sent encore la pomme.
+narrateur|Un toc lointain, sous la table.
+narrateur|Il ne reste plus rien dans le bol.
+narrateur|La casserole fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -15858,12 +16058,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous le tabouret. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. La voiture reprend toc.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Je pousse. Moi, je dis les arrêts. Raphaël pousse la voiture. Mila annonce. Prochain : les assiettes. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>On attend. La pomme tremble, puis s'arrête. Elle reste sous le tabouret. Elle ne fuit plus. Vous avez laissé le temps. Raphaël avance deux doigts. La pomme roule dans sa paume. Merci d'avoir attendu. On la remet. La voiture reprend toc.</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -15926,7 +16126,7 @@
         <v>0.92</v>
       </c>
       <c r="AB84" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
@@ -15998,15 +16198,16 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>enfant-m|Je pousse.
-enfant-f|Moi, je dis les arrêts.
-narrateur|Raphaël pousse la voiture. Mila annonce.
-enfant-f|Prochain : les assiettes.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-m|On attend.
+narrateur|La pomme tremble, puis s'arrête.
+narrateur|Elle reste sous le tabouret.
+enfant-f|Elle ne fuit plus.
+papa|Vous avez laissé le temps.
+narrateur|Raphaël avance deux doigts.
+narrateur|La pomme roule dans sa paume.
+enfant-m|Merci d'avoir attendu.
+enfant-f|On la remet.
+narrateur|La voiture reprend toc.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
@@ -16038,12 +16239,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. Le tabouret garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>La voiture rejoint les assiettes, sans se presser. Ils croquent, tout doux. Elle a attendu, elle aussi. Le voyage a pris le temps qu'il faut. Le marché, dehors, s'est calmé. Une rondelle brille encore au fond. Le tabouret garde une petite ombre mouillée. Papa raccroche le torchon rayé. Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -16099,14 +16300,14 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA85" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB85" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
@@ -16178,11 +16379,15 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|La voiture descend du tabouret.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|La voiture rejoint les assiettes, sans se presser.
+narrateur|Ils croquent, tout doux.
+enfant-f|Elle a attendu, elle aussi.
+papa|Le voyage a pris le temps qu'il faut.
+maman|Le marché, dehors, s'est calmé.
+narrateur|Une rondelle brille encore au fond.
+narrateur|Le tabouret garde une petite ombre mouillée.
+narrateur|Papa raccroche le torchon rayé.
+narrateur|Ça sent encore le fruit, près de l'évier.</t>
         </is>
       </c>
     </row>
@@ -16209,12 +16414,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous le tabouret, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Ensemble. Toi devant. Moi derrière. Ils poussent la voiture avec quatre mains. Le bol avance. Une rondelle tremble, puis tient. Terminus, les pommes. Ils posent une rondelle chacun. On croque. Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>C'est l'invitée en retard. Le restaurant ouvre pour elle. Ils posent la pomme sous le tabouret, comme un siège. S'il te plaît, une rondelle. Voilà, madame Pomme. Une table pour trois, alors. Mila glisse une rondelle près de la ronde. Raphaël verse un peu d'eau dans un gobelet. Merci d'être venue. La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -16277,7 +16482,7 @@
         <v>0.92</v>
       </c>
       <c r="AB86" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
@@ -16349,14 +16554,16 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>enfant-m|Ensemble.
-enfant-f|Toi devant. Moi derrière.
-narrateur|Ils poussent la voiture avec quatre mains.
-narrateur|Le bol avance. Une rondelle tremble, puis tient.
-enfant-m|Terminus, les pommes.
-narrateur|Ils posent une rondelle chacun.
-enfant-f|On croque.
-narrateur|Ça croque, tout doux. Ça sent encore le fruit.</t>
+          <t>enfant-f|C'est l'invitée en retard.
+enfant-m|Le restaurant ouvre pour elle.
+narrateur|Ils posent la pomme sous le tabouret, comme un siège.
+enfant-f|S'il te plaît, une rondelle.
+enfant-m|Voilà, madame Pomme.
+papa|Une table pour trois, alors.
+narrateur|Mila glisse une rondelle près de la ronde.
+narrateur|Raphaël verse un peu d'eau dans un gobelet.
+enfant-f|Merci d'être venue.
+narrateur|La voiture fait le vestiaire.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -16388,12 +16595,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. La voiture dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>La voiture descend du tabouret. Cargaison livrée. Vous avez fait le voyage. Les assiettes sont vides, maintenant. L'histoire est finie.</t>
+          <t>L'invitée a une goutte sur la peau. On l'a gardée pour la fin. On la partage. Papa coupe la pomme ronde en deux. Il en reste pour demain, sur le torchon. La voiture dort près du bol. Plus rien ne cache le carrelage. Le soleil a bougé sur le carrelage. Dehors, le marché a fermé.</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -16449,14 +16656,14 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA87" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB87" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
@@ -16528,11 +16735,15 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|La voiture descend du tabouret.
-enfant-m|Cargaison livrée.
-papa|Vous avez fait le voyage.
-narrateur|Les assiettes sont vides, maintenant.
-narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'invitée a une goutte sur la peau.
+enfant-m|On l'a gardée pour la fin.
+enfant-f|On la partage.
+narrateur|Papa coupe la pomme ronde en deux.
+maman|Il en reste pour demain, sur le torchon.
+narrateur|La voiture dort près du bol.
+narrateur|Plus rien ne cache le carrelage.
+narrateur|Le soleil a bougé sur le carrelage.
+narrateur|Dehors, le marché a fermé.</t>
         </is>
       </c>
     </row>
@@ -16553,7 +16764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16631,6 +16842,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
